--- a/fazla_mesai_cizelge.xlsx
+++ b/fazla_mesai_cizelge.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Documents\Mesai Programı\app\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Documents\Mesai Programı APK\web-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E8A7E2-11E1-4232-95DD-A577616B9ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAEBA54F-4ACF-41A9-AFDC-7B2E790671ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{226E1638-84E9-4960-B4B3-419E2FB407AE}"/>
   </bookViews>
@@ -381,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -466,44 +466,38 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -834,36 +828,36 @@
       <c r="A1" s="20"/>
       <c r="B1" s="20"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
       <c r="AF1" s="6"/>
       <c r="AG1" s="6"/>
       <c r="AH1" s="6"/>
@@ -877,36 +871,36 @@
       <c r="A2" s="20"/>
       <c r="B2" s="20"/>
       <c r="C2" s="6"/>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
       <c r="AF2" s="6"/>
       <c r="AG2" s="6"/>
       <c r="AH2" s="6"/>
@@ -1033,11 +1027,11 @@
       </c>
     </row>
     <row r="4" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42">
+      <c r="A4" s="32">
         <v>1</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
       <c r="D4" s="23">
         <v>0.6</v>
       </c>
@@ -1073,13 +1067,13 @@
       <c r="AH4" s="8"/>
       <c r="AI4" s="9"/>
       <c r="AJ4" s="10"/>
-      <c r="AK4" s="39"/>
-      <c r="AL4" s="39"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
     </row>
     <row r="5" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="38"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="24">
         <v>0.15</v>
       </c>
@@ -1115,16 +1109,16 @@
       <c r="AH5" s="11"/>
       <c r="AI5" s="12"/>
       <c r="AJ5" s="13"/>
-      <c r="AK5" s="36"/>
-      <c r="AL5" s="36"/>
+      <c r="AK5" s="37"/>
+      <c r="AL5" s="37"/>
       <c r="AQ5" s="4"/>
     </row>
     <row r="6" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42">
+      <c r="A6" s="32">
         <v>2</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="23">
         <v>0.6</v>
       </c>
@@ -1160,13 +1154,13 @@
       <c r="AH6" s="8"/>
       <c r="AI6" s="9"/>
       <c r="AJ6" s="10"/>
-      <c r="AK6" s="39"/>
-      <c r="AL6" s="39"/>
+      <c r="AK6" s="36"/>
+      <c r="AL6" s="36"/>
     </row>
     <row r="7" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="38"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="24">
         <v>0.15</v>
       </c>
@@ -1202,16 +1196,16 @@
       <c r="AH7" s="11"/>
       <c r="AI7" s="12"/>
       <c r="AJ7" s="13"/>
-      <c r="AK7" s="36"/>
-      <c r="AL7" s="36"/>
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="37"/>
       <c r="AQ7" s="4"/>
     </row>
     <row r="8" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="42">
+      <c r="A8" s="32">
         <v>3</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
       <c r="D8" s="23">
         <v>0.6</v>
       </c>
@@ -1247,13 +1241,13 @@
       <c r="AH8" s="8"/>
       <c r="AI8" s="9"/>
       <c r="AJ8" s="10"/>
-      <c r="AK8" s="39"/>
-      <c r="AL8" s="39"/>
+      <c r="AK8" s="36"/>
+      <c r="AL8" s="36"/>
     </row>
     <row r="9" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="38"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="24">
         <v>0.15</v>
       </c>
@@ -1289,16 +1283,16 @@
       <c r="AH9" s="11"/>
       <c r="AI9" s="12"/>
       <c r="AJ9" s="13"/>
-      <c r="AK9" s="36"/>
-      <c r="AL9" s="36"/>
+      <c r="AK9" s="37"/>
+      <c r="AL9" s="37"/>
       <c r="AQ9" s="4"/>
     </row>
     <row r="10" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="42">
+      <c r="A10" s="32">
         <v>4</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="41"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="23">
         <v>0.6</v>
       </c>
@@ -1334,13 +1328,13 @@
       <c r="AH10" s="8"/>
       <c r="AI10" s="9"/>
       <c r="AJ10" s="10"/>
-      <c r="AK10" s="39"/>
-      <c r="AL10" s="39"/>
+      <c r="AK10" s="36"/>
+      <c r="AL10" s="36"/>
     </row>
     <row r="11" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="38"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="24">
         <v>0.15</v>
       </c>
@@ -1376,16 +1370,16 @@
       <c r="AH11" s="11"/>
       <c r="AI11" s="12"/>
       <c r="AJ11" s="13"/>
-      <c r="AK11" s="36"/>
-      <c r="AL11" s="36"/>
+      <c r="AK11" s="37"/>
+      <c r="AL11" s="37"/>
       <c r="AQ11" s="4"/>
     </row>
     <row r="12" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="42">
+      <c r="A12" s="32">
         <v>5</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="23">
         <v>0.6</v>
       </c>
@@ -1421,13 +1415,13 @@
       <c r="AH12" s="8"/>
       <c r="AI12" s="9"/>
       <c r="AJ12" s="10"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
+      <c r="AK12" s="36"/>
+      <c r="AL12" s="36"/>
     </row>
     <row r="13" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="38"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="24">
         <v>0.15</v>
       </c>
@@ -1463,16 +1457,16 @@
       <c r="AH13" s="11"/>
       <c r="AI13" s="12"/>
       <c r="AJ13" s="13"/>
-      <c r="AK13" s="36"/>
-      <c r="AL13" s="36"/>
+      <c r="AK13" s="37"/>
+      <c r="AL13" s="37"/>
       <c r="AQ13" s="4"/>
     </row>
     <row r="14" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="42">
+      <c r="A14" s="32">
         <v>6</v>
       </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="23">
         <v>0.6</v>
       </c>
@@ -1508,13 +1502,13 @@
       <c r="AH14" s="8"/>
       <c r="AI14" s="9"/>
       <c r="AJ14" s="10"/>
-      <c r="AK14" s="39"/>
-      <c r="AL14" s="39"/>
+      <c r="AK14" s="36"/>
+      <c r="AL14" s="36"/>
     </row>
     <row r="15" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="43"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="38"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="24">
         <v>0.15</v>
       </c>
@@ -1550,16 +1544,16 @@
       <c r="AH15" s="11"/>
       <c r="AI15" s="12"/>
       <c r="AJ15" s="13"/>
-      <c r="AK15" s="36"/>
-      <c r="AL15" s="36"/>
+      <c r="AK15" s="37"/>
+      <c r="AL15" s="37"/>
       <c r="AQ15" s="4"/>
     </row>
     <row r="16" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="42">
+      <c r="A16" s="32">
         <v>7</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="23">
         <v>0.6</v>
       </c>
@@ -1595,13 +1589,13 @@
       <c r="AH16" s="8"/>
       <c r="AI16" s="9"/>
       <c r="AJ16" s="10"/>
-      <c r="AK16" s="39"/>
-      <c r="AL16" s="39"/>
+      <c r="AK16" s="36"/>
+      <c r="AL16" s="36"/>
     </row>
     <row r="17" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="38"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
       <c r="D17" s="24">
         <v>0.15</v>
       </c>
@@ -1637,16 +1631,16 @@
       <c r="AH17" s="11"/>
       <c r="AI17" s="12"/>
       <c r="AJ17" s="13"/>
-      <c r="AK17" s="36"/>
-      <c r="AL17" s="36"/>
+      <c r="AK17" s="37"/>
+      <c r="AL17" s="37"/>
       <c r="AQ17" s="4"/>
     </row>
     <row r="18" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="42">
+      <c r="A18" s="32">
         <v>8</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
       <c r="D18" s="23">
         <v>0.6</v>
       </c>
@@ -1682,13 +1676,13 @@
       <c r="AH18" s="8"/>
       <c r="AI18" s="9"/>
       <c r="AJ18" s="10"/>
-      <c r="AK18" s="39"/>
-      <c r="AL18" s="39"/>
+      <c r="AK18" s="36"/>
+      <c r="AL18" s="36"/>
     </row>
     <row r="19" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="43"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="38"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
       <c r="D19" s="24">
         <v>0.15</v>
       </c>
@@ -1724,16 +1718,16 @@
       <c r="AH19" s="11"/>
       <c r="AI19" s="12"/>
       <c r="AJ19" s="13"/>
-      <c r="AK19" s="36"/>
-      <c r="AL19" s="36"/>
+      <c r="AK19" s="37"/>
+      <c r="AL19" s="37"/>
       <c r="AQ19" s="4"/>
     </row>
     <row r="20" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42">
+      <c r="A20" s="32">
         <v>9</v>
       </c>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
       <c r="D20" s="23">
         <v>0.6</v>
       </c>
@@ -1769,13 +1763,13 @@
       <c r="AH20" s="8"/>
       <c r="AI20" s="9"/>
       <c r="AJ20" s="10"/>
-      <c r="AK20" s="39"/>
-      <c r="AL20" s="39"/>
+      <c r="AK20" s="36"/>
+      <c r="AL20" s="36"/>
     </row>
     <row r="21" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="43"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="38"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
       <c r="D21" s="24">
         <v>0.15</v>
       </c>
@@ -1811,16 +1805,16 @@
       <c r="AH21" s="11"/>
       <c r="AI21" s="12"/>
       <c r="AJ21" s="13"/>
-      <c r="AK21" s="36"/>
-      <c r="AL21" s="36"/>
+      <c r="AK21" s="37"/>
+      <c r="AL21" s="37"/>
       <c r="AQ21" s="4"/>
     </row>
     <row r="22" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="42">
+      <c r="A22" s="32">
         <v>10</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
       <c r="D22" s="23">
         <v>0.6</v>
       </c>
@@ -1856,13 +1850,13 @@
       <c r="AH22" s="8"/>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="10"/>
-      <c r="AK22" s="39"/>
-      <c r="AL22" s="39"/>
+      <c r="AK22" s="36"/>
+      <c r="AL22" s="36"/>
     </row>
     <row r="23" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="43"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="38"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="24">
         <v>0.15</v>
       </c>
@@ -1898,16 +1892,16 @@
       <c r="AH23" s="11"/>
       <c r="AI23" s="12"/>
       <c r="AJ23" s="13"/>
-      <c r="AK23" s="36"/>
-      <c r="AL23" s="36"/>
+      <c r="AK23" s="37"/>
+      <c r="AL23" s="37"/>
       <c r="AQ23" s="4"/>
     </row>
     <row r="24" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="42">
+      <c r="A24" s="32">
         <v>11</v>
       </c>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
       <c r="D24" s="23">
         <v>0.6</v>
       </c>
@@ -1943,13 +1937,13 @@
       <c r="AH24" s="8"/>
       <c r="AI24" s="9"/>
       <c r="AJ24" s="10"/>
-      <c r="AK24" s="39"/>
-      <c r="AL24" s="39"/>
+      <c r="AK24" s="36"/>
+      <c r="AL24" s="36"/>
     </row>
     <row r="25" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="38"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
       <c r="D25" s="24">
         <v>0.15</v>
       </c>
@@ -1985,16 +1979,16 @@
       <c r="AH25" s="11"/>
       <c r="AI25" s="12"/>
       <c r="AJ25" s="13"/>
-      <c r="AK25" s="36"/>
-      <c r="AL25" s="36"/>
+      <c r="AK25" s="37"/>
+      <c r="AL25" s="37"/>
       <c r="AQ25" s="4"/>
     </row>
     <row r="26" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="42">
+      <c r="A26" s="32">
         <v>12</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
       <c r="D26" s="23">
         <v>0.6</v>
       </c>
@@ -2030,13 +2024,13 @@
       <c r="AH26" s="8"/>
       <c r="AI26" s="9"/>
       <c r="AJ26" s="10"/>
-      <c r="AK26" s="39"/>
-      <c r="AL26" s="39"/>
+      <c r="AK26" s="36"/>
+      <c r="AL26" s="36"/>
     </row>
     <row r="27" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="43"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="38"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
       <c r="D27" s="24">
         <v>0.15</v>
       </c>
@@ -2072,16 +2066,16 @@
       <c r="AH27" s="11"/>
       <c r="AI27" s="12"/>
       <c r="AJ27" s="13"/>
-      <c r="AK27" s="36"/>
-      <c r="AL27" s="36"/>
+      <c r="AK27" s="37"/>
+      <c r="AL27" s="37"/>
       <c r="AQ27" s="4"/>
     </row>
     <row r="28" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="42">
+      <c r="A28" s="32">
         <v>13</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="41"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
       <c r="D28" s="23">
         <v>0.6</v>
       </c>
@@ -2117,13 +2111,13 @@
       <c r="AH28" s="8"/>
       <c r="AI28" s="9"/>
       <c r="AJ28" s="10"/>
-      <c r="AK28" s="39"/>
-      <c r="AL28" s="39"/>
+      <c r="AK28" s="36"/>
+      <c r="AL28" s="36"/>
     </row>
     <row r="29" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="43"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="38"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
       <c r="D29" s="24">
         <v>0.15</v>
       </c>
@@ -2159,16 +2153,16 @@
       <c r="AH29" s="11"/>
       <c r="AI29" s="12"/>
       <c r="AJ29" s="13"/>
-      <c r="AK29" s="36"/>
-      <c r="AL29" s="36"/>
+      <c r="AK29" s="37"/>
+      <c r="AL29" s="37"/>
       <c r="AQ29" s="4"/>
     </row>
     <row r="30" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="42">
+      <c r="A30" s="32">
         <v>14</v>
       </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
       <c r="D30" s="23">
         <v>0.6</v>
       </c>
@@ -2204,13 +2198,13 @@
       <c r="AH30" s="8"/>
       <c r="AI30" s="9"/>
       <c r="AJ30" s="10"/>
-      <c r="AK30" s="39"/>
-      <c r="AL30" s="39"/>
+      <c r="AK30" s="36"/>
+      <c r="AL30" s="36"/>
     </row>
     <row r="31" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="43"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="38"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
       <c r="D31" s="24">
         <v>0.15</v>
       </c>
@@ -2246,16 +2240,16 @@
       <c r="AH31" s="11"/>
       <c r="AI31" s="12"/>
       <c r="AJ31" s="13"/>
-      <c r="AK31" s="36"/>
-      <c r="AL31" s="36"/>
+      <c r="AK31" s="37"/>
+      <c r="AL31" s="37"/>
       <c r="AQ31" s="4"/>
     </row>
     <row r="32" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="42">
+      <c r="A32" s="32">
         <v>15</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="41"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
       <c r="D32" s="23">
         <v>0.6</v>
       </c>
@@ -2291,13 +2285,13 @@
       <c r="AH32" s="8"/>
       <c r="AI32" s="9"/>
       <c r="AJ32" s="10"/>
-      <c r="AK32" s="39"/>
-      <c r="AL32" s="39"/>
+      <c r="AK32" s="36"/>
+      <c r="AL32" s="36"/>
     </row>
     <row r="33" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="43"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="38"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
       <c r="D33" s="24">
         <v>0.15</v>
       </c>
@@ -2333,16 +2327,16 @@
       <c r="AH33" s="11"/>
       <c r="AI33" s="12"/>
       <c r="AJ33" s="13"/>
-      <c r="AK33" s="36"/>
-      <c r="AL33" s="36"/>
+      <c r="AK33" s="37"/>
+      <c r="AL33" s="37"/>
       <c r="AQ33" s="4"/>
     </row>
     <row r="34" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="42">
+      <c r="A34" s="32">
         <v>16</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="41"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
       <c r="D34" s="23">
         <v>0.6</v>
       </c>
@@ -2378,13 +2372,13 @@
       <c r="AH34" s="8"/>
       <c r="AI34" s="9"/>
       <c r="AJ34" s="10"/>
-      <c r="AK34" s="39"/>
-      <c r="AL34" s="39"/>
+      <c r="AK34" s="36"/>
+      <c r="AL34" s="36"/>
     </row>
     <row r="35" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="43"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="38"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
       <c r="D35" s="24">
         <v>0.15</v>
       </c>
@@ -2420,16 +2414,16 @@
       <c r="AH35" s="11"/>
       <c r="AI35" s="12"/>
       <c r="AJ35" s="13"/>
-      <c r="AK35" s="36"/>
-      <c r="AL35" s="36"/>
+      <c r="AK35" s="37"/>
+      <c r="AL35" s="37"/>
       <c r="AQ35" s="4"/>
     </row>
     <row r="36" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="42">
+      <c r="A36" s="32">
         <v>17</v>
       </c>
-      <c r="B36" s="40"/>
-      <c r="C36" s="41"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
       <c r="D36" s="23">
         <v>0.6</v>
       </c>
@@ -2465,13 +2459,13 @@
       <c r="AH36" s="8"/>
       <c r="AI36" s="9"/>
       <c r="AJ36" s="10"/>
-      <c r="AK36" s="39"/>
-      <c r="AL36" s="39"/>
+      <c r="AK36" s="36"/>
+      <c r="AL36" s="36"/>
     </row>
     <row r="37" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="43"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="38"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
       <c r="D37" s="24">
         <v>0.15</v>
       </c>
@@ -2507,16 +2501,16 @@
       <c r="AH37" s="11"/>
       <c r="AI37" s="12"/>
       <c r="AJ37" s="13"/>
-      <c r="AK37" s="36"/>
-      <c r="AL37" s="36"/>
+      <c r="AK37" s="37"/>
+      <c r="AL37" s="37"/>
       <c r="AQ37" s="4"/>
     </row>
     <row r="38" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="42">
+      <c r="A38" s="32">
         <v>18</v>
       </c>
-      <c r="B38" s="40"/>
-      <c r="C38" s="41"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
       <c r="D38" s="23">
         <v>0.6</v>
       </c>
@@ -2552,13 +2546,13 @@
       <c r="AH38" s="8"/>
       <c r="AI38" s="9"/>
       <c r="AJ38" s="10"/>
-      <c r="AK38" s="39"/>
-      <c r="AL38" s="39"/>
+      <c r="AK38" s="36"/>
+      <c r="AL38" s="36"/>
     </row>
     <row r="39" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="43"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="38"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
       <c r="D39" s="24">
         <v>0.15</v>
       </c>
@@ -2594,16 +2588,16 @@
       <c r="AH39" s="11"/>
       <c r="AI39" s="12"/>
       <c r="AJ39" s="13"/>
-      <c r="AK39" s="36"/>
-      <c r="AL39" s="36"/>
+      <c r="AK39" s="37"/>
+      <c r="AL39" s="37"/>
       <c r="AQ39" s="4"/>
     </row>
     <row r="40" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="42">
+      <c r="A40" s="32">
         <v>19</v>
       </c>
-      <c r="B40" s="40"/>
-      <c r="C40" s="41"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
       <c r="D40" s="23">
         <v>0.6</v>
       </c>
@@ -2639,13 +2633,13 @@
       <c r="AH40" s="8"/>
       <c r="AI40" s="9"/>
       <c r="AJ40" s="10"/>
-      <c r="AK40" s="39"/>
-      <c r="AL40" s="39"/>
+      <c r="AK40" s="36"/>
+      <c r="AL40" s="36"/>
     </row>
     <row r="41" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="43"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="38"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="35"/>
       <c r="D41" s="24">
         <v>0.15</v>
       </c>
@@ -2681,16 +2675,16 @@
       <c r="AH41" s="11"/>
       <c r="AI41" s="12"/>
       <c r="AJ41" s="13"/>
-      <c r="AK41" s="36"/>
-      <c r="AL41" s="36"/>
+      <c r="AK41" s="37"/>
+      <c r="AL41" s="37"/>
       <c r="AQ41" s="4"/>
     </row>
     <row r="42" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="42">
+      <c r="A42" s="32">
         <v>20</v>
       </c>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
       <c r="D42" s="23">
         <v>0.6</v>
       </c>
@@ -2726,13 +2720,13 @@
       <c r="AH42" s="8"/>
       <c r="AI42" s="9"/>
       <c r="AJ42" s="10"/>
-      <c r="AK42" s="39"/>
-      <c r="AL42" s="39"/>
+      <c r="AK42" s="36"/>
+      <c r="AL42" s="36"/>
     </row>
     <row r="43" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="43"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="38"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="35"/>
       <c r="D43" s="24">
         <v>0.15</v>
       </c>
@@ -2768,16 +2762,16 @@
       <c r="AH43" s="11"/>
       <c r="AI43" s="12"/>
       <c r="AJ43" s="13"/>
-      <c r="AK43" s="36"/>
-      <c r="AL43" s="36"/>
+      <c r="AK43" s="37"/>
+      <c r="AL43" s="37"/>
       <c r="AQ43" s="4"/>
     </row>
     <row r="44" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="42">
+      <c r="A44" s="32">
         <v>21</v>
       </c>
-      <c r="B44" s="40"/>
-      <c r="C44" s="41"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
       <c r="D44" s="23">
         <v>0.6</v>
       </c>
@@ -2813,13 +2807,13 @@
       <c r="AH44" s="8"/>
       <c r="AI44" s="9"/>
       <c r="AJ44" s="10"/>
-      <c r="AK44" s="39"/>
-      <c r="AL44" s="39"/>
+      <c r="AK44" s="36"/>
+      <c r="AL44" s="36"/>
     </row>
     <row r="45" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="43"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="38"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="35"/>
+      <c r="C45" s="35"/>
       <c r="D45" s="24">
         <v>0.15</v>
       </c>
@@ -2855,16 +2849,16 @@
       <c r="AH45" s="11"/>
       <c r="AI45" s="12"/>
       <c r="AJ45" s="13"/>
-      <c r="AK45" s="36"/>
-      <c r="AL45" s="36"/>
+      <c r="AK45" s="37"/>
+      <c r="AL45" s="37"/>
       <c r="AQ45" s="4"/>
     </row>
     <row r="46" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="42">
+      <c r="A46" s="32">
         <v>22</v>
       </c>
-      <c r="B46" s="40"/>
-      <c r="C46" s="41"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
       <c r="D46" s="23">
         <v>0.6</v>
       </c>
@@ -2900,13 +2894,13 @@
       <c r="AH46" s="8"/>
       <c r="AI46" s="9"/>
       <c r="AJ46" s="10"/>
-      <c r="AK46" s="39"/>
-      <c r="AL46" s="39"/>
+      <c r="AK46" s="36"/>
+      <c r="AL46" s="36"/>
     </row>
     <row r="47" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="43"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="38"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="35"/>
+      <c r="C47" s="35"/>
       <c r="D47" s="24">
         <v>0.15</v>
       </c>
@@ -2942,16 +2936,16 @@
       <c r="AH47" s="11"/>
       <c r="AI47" s="12"/>
       <c r="AJ47" s="13"/>
-      <c r="AK47" s="36"/>
-      <c r="AL47" s="36"/>
+      <c r="AK47" s="37"/>
+      <c r="AL47" s="37"/>
       <c r="AQ47" s="4"/>
     </row>
     <row r="48" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="42">
+      <c r="A48" s="32">
         <v>23</v>
       </c>
-      <c r="B48" s="40"/>
-      <c r="C48" s="41"/>
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
       <c r="D48" s="23">
         <v>0.6</v>
       </c>
@@ -2987,13 +2981,13 @@
       <c r="AH48" s="8"/>
       <c r="AI48" s="9"/>
       <c r="AJ48" s="10"/>
-      <c r="AK48" s="39"/>
-      <c r="AL48" s="39"/>
+      <c r="AK48" s="36"/>
+      <c r="AL48" s="36"/>
     </row>
     <row r="49" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="43"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="38"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="35"/>
       <c r="D49" s="24">
         <v>0.15</v>
       </c>
@@ -3029,16 +3023,16 @@
       <c r="AH49" s="11"/>
       <c r="AI49" s="12"/>
       <c r="AJ49" s="13"/>
-      <c r="AK49" s="36"/>
-      <c r="AL49" s="36"/>
+      <c r="AK49" s="37"/>
+      <c r="AL49" s="37"/>
       <c r="AQ49" s="4"/>
     </row>
     <row r="50" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="42">
+      <c r="A50" s="32">
         <v>24</v>
       </c>
-      <c r="B50" s="40"/>
-      <c r="C50" s="41"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="34"/>
       <c r="D50" s="23">
         <v>0.6</v>
       </c>
@@ -3074,13 +3068,13 @@
       <c r="AH50" s="8"/>
       <c r="AI50" s="9"/>
       <c r="AJ50" s="10"/>
-      <c r="AK50" s="39"/>
-      <c r="AL50" s="39"/>
+      <c r="AK50" s="36"/>
+      <c r="AL50" s="36"/>
     </row>
     <row r="51" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="43"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="38"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="35"/>
       <c r="D51" s="24">
         <v>0.15</v>
       </c>
@@ -3116,16 +3110,16 @@
       <c r="AH51" s="11"/>
       <c r="AI51" s="12"/>
       <c r="AJ51" s="13"/>
-      <c r="AK51" s="36"/>
-      <c r="AL51" s="36"/>
+      <c r="AK51" s="37"/>
+      <c r="AL51" s="37"/>
       <c r="AQ51" s="4"/>
     </row>
     <row r="52" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="42">
+      <c r="A52" s="32">
         <v>25</v>
       </c>
-      <c r="B52" s="33"/>
-      <c r="C52" s="37"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
       <c r="D52" s="23">
         <v>0.6</v>
       </c>
@@ -3161,13 +3155,13 @@
       <c r="AH52" s="8"/>
       <c r="AI52" s="9"/>
       <c r="AJ52" s="10"/>
-      <c r="AK52" s="35"/>
-      <c r="AL52" s="35"/>
+      <c r="AK52" s="39"/>
+      <c r="AL52" s="39"/>
     </row>
     <row r="53" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="43"/>
-      <c r="B53" s="34"/>
-      <c r="C53" s="38"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="24">
         <v>0.15</v>
       </c>
@@ -3203,16 +3197,16 @@
       <c r="AH53" s="11"/>
       <c r="AI53" s="12"/>
       <c r="AJ53" s="13"/>
-      <c r="AK53" s="36"/>
-      <c r="AL53" s="36"/>
+      <c r="AK53" s="37"/>
+      <c r="AL53" s="37"/>
       <c r="AQ53" s="4"/>
     </row>
     <row r="54" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="42">
+      <c r="A54" s="32">
         <v>26</v>
       </c>
-      <c r="B54" s="33"/>
-      <c r="C54" s="37"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
       <c r="D54" s="23">
         <v>0.6</v>
       </c>
@@ -3248,13 +3242,13 @@
       <c r="AH54" s="8"/>
       <c r="AI54" s="9"/>
       <c r="AJ54" s="10"/>
-      <c r="AK54" s="35"/>
-      <c r="AL54" s="35"/>
+      <c r="AK54" s="39"/>
+      <c r="AL54" s="39"/>
     </row>
     <row r="55" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="43"/>
-      <c r="B55" s="34"/>
-      <c r="C55" s="38"/>
+      <c r="A55" s="33"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="35"/>
       <c r="D55" s="24">
         <v>0.15</v>
       </c>
@@ -3290,25 +3284,25 @@
       <c r="AH55" s="11"/>
       <c r="AI55" s="12"/>
       <c r="AJ55" s="13"/>
-      <c r="AK55" s="36"/>
-      <c r="AL55" s="36"/>
+      <c r="AK55" s="37"/>
+      <c r="AL55" s="37"/>
       <c r="AQ55" s="4"/>
     </row>
     <row r="56" spans="1:43" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="1"/>
+      <c r="C56" s="42"/>
       <c r="D56" s="25" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="42">
+      <c r="A57" s="32">
         <v>27</v>
       </c>
-      <c r="B57" s="40"/>
-      <c r="C57" s="41"/>
+      <c r="B57" s="34"/>
+      <c r="C57" s="34"/>
       <c r="D57" s="23">
         <v>0.6</v>
       </c>
@@ -3344,13 +3338,13 @@
       <c r="AH57" s="8"/>
       <c r="AI57" s="9"/>
       <c r="AJ57" s="10"/>
-      <c r="AK57" s="39"/>
-      <c r="AL57" s="39"/>
+      <c r="AK57" s="36"/>
+      <c r="AL57" s="36"/>
     </row>
     <row r="58" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="43"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="38"/>
+      <c r="A58" s="33"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
       <c r="D58" s="24">
         <v>0.15</v>
       </c>
@@ -3386,16 +3380,16 @@
       <c r="AH58" s="11"/>
       <c r="AI58" s="12"/>
       <c r="AJ58" s="13"/>
-      <c r="AK58" s="36"/>
-      <c r="AL58" s="36"/>
+      <c r="AK58" s="37"/>
+      <c r="AL58" s="37"/>
       <c r="AQ58" s="4"/>
     </row>
     <row r="59" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="42">
+      <c r="A59" s="32">
         <v>28</v>
       </c>
-      <c r="B59" s="40"/>
-      <c r="C59" s="41"/>
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
       <c r="D59" s="23">
         <v>0.6</v>
       </c>
@@ -3431,13 +3425,13 @@
       <c r="AH59" s="8"/>
       <c r="AI59" s="9"/>
       <c r="AJ59" s="10"/>
-      <c r="AK59" s="39"/>
-      <c r="AL59" s="39"/>
+      <c r="AK59" s="36"/>
+      <c r="AL59" s="36"/>
     </row>
     <row r="60" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="43"/>
-      <c r="B60" s="34"/>
-      <c r="C60" s="38"/>
+      <c r="A60" s="33"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="35"/>
       <c r="D60" s="24">
         <v>0.15</v>
       </c>
@@ -3473,16 +3467,16 @@
       <c r="AH60" s="11"/>
       <c r="AI60" s="12"/>
       <c r="AJ60" s="13"/>
-      <c r="AK60" s="36"/>
-      <c r="AL60" s="36"/>
+      <c r="AK60" s="37"/>
+      <c r="AL60" s="37"/>
       <c r="AQ60" s="4"/>
     </row>
     <row r="61" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="42">
+      <c r="A61" s="32">
         <v>29</v>
       </c>
-      <c r="B61" s="40"/>
-      <c r="C61" s="41"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
       <c r="D61" s="23">
         <v>0.6</v>
       </c>
@@ -3518,13 +3512,13 @@
       <c r="AH61" s="8"/>
       <c r="AI61" s="9"/>
       <c r="AJ61" s="10"/>
-      <c r="AK61" s="39"/>
-      <c r="AL61" s="39"/>
+      <c r="AK61" s="36"/>
+      <c r="AL61" s="36"/>
     </row>
     <row r="62" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="43"/>
-      <c r="B62" s="34"/>
-      <c r="C62" s="38"/>
+      <c r="A62" s="33"/>
+      <c r="B62" s="35"/>
+      <c r="C62" s="35"/>
       <c r="D62" s="24">
         <v>0.15</v>
       </c>
@@ -3560,16 +3554,16 @@
       <c r="AH62" s="11"/>
       <c r="AI62" s="12"/>
       <c r="AJ62" s="13"/>
-      <c r="AK62" s="36"/>
-      <c r="AL62" s="36"/>
+      <c r="AK62" s="37"/>
+      <c r="AL62" s="37"/>
       <c r="AQ62" s="4"/>
     </row>
     <row r="63" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="42">
+      <c r="A63" s="32">
         <v>30</v>
       </c>
-      <c r="B63" s="40"/>
-      <c r="C63" s="41"/>
+      <c r="B63" s="34"/>
+      <c r="C63" s="34"/>
       <c r="D63" s="23">
         <v>0.6</v>
       </c>
@@ -3605,13 +3599,13 @@
       <c r="AH63" s="8"/>
       <c r="AI63" s="9"/>
       <c r="AJ63" s="10"/>
-      <c r="AK63" s="39"/>
-      <c r="AL63" s="39"/>
+      <c r="AK63" s="36"/>
+      <c r="AL63" s="36"/>
     </row>
     <row r="64" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="43"/>
-      <c r="B64" s="34"/>
-      <c r="C64" s="38"/>
+      <c r="A64" s="33"/>
+      <c r="B64" s="35"/>
+      <c r="C64" s="35"/>
       <c r="D64" s="24">
         <v>0.15</v>
       </c>
@@ -3647,16 +3641,16 @@
       <c r="AH64" s="11"/>
       <c r="AI64" s="12"/>
       <c r="AJ64" s="13"/>
-      <c r="AK64" s="36"/>
-      <c r="AL64" s="36"/>
+      <c r="AK64" s="37"/>
+      <c r="AL64" s="37"/>
       <c r="AQ64" s="4"/>
     </row>
     <row r="65" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="42">
+      <c r="A65" s="32">
         <v>31</v>
       </c>
-      <c r="B65" s="40"/>
-      <c r="C65" s="41"/>
+      <c r="B65" s="34"/>
+      <c r="C65" s="34"/>
       <c r="D65" s="23">
         <v>0.6</v>
       </c>
@@ -3692,13 +3686,13 @@
       <c r="AH65" s="8"/>
       <c r="AI65" s="9"/>
       <c r="AJ65" s="10"/>
-      <c r="AK65" s="39"/>
-      <c r="AL65" s="39"/>
+      <c r="AK65" s="36"/>
+      <c r="AL65" s="36"/>
     </row>
     <row r="66" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="43"/>
-      <c r="B66" s="34"/>
-      <c r="C66" s="38"/>
+      <c r="A66" s="33"/>
+      <c r="B66" s="35"/>
+      <c r="C66" s="35"/>
       <c r="D66" s="24">
         <v>0.15</v>
       </c>
@@ -3734,16 +3728,16 @@
       <c r="AH66" s="11"/>
       <c r="AI66" s="12"/>
       <c r="AJ66" s="13"/>
-      <c r="AK66" s="36"/>
-      <c r="AL66" s="36"/>
+      <c r="AK66" s="37"/>
+      <c r="AL66" s="37"/>
       <c r="AQ66" s="4"/>
     </row>
     <row r="67" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="42">
+      <c r="A67" s="32">
         <v>32</v>
       </c>
-      <c r="B67" s="40"/>
-      <c r="C67" s="41"/>
+      <c r="B67" s="34"/>
+      <c r="C67" s="34"/>
       <c r="D67" s="23">
         <v>0.6</v>
       </c>
@@ -3779,13 +3773,13 @@
       <c r="AH67" s="8"/>
       <c r="AI67" s="9"/>
       <c r="AJ67" s="10"/>
-      <c r="AK67" s="39"/>
-      <c r="AL67" s="39"/>
+      <c r="AK67" s="36"/>
+      <c r="AL67" s="36"/>
     </row>
     <row r="68" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="43"/>
-      <c r="B68" s="34"/>
-      <c r="C68" s="38"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="35"/>
+      <c r="C68" s="35"/>
       <c r="D68" s="24">
         <v>0.15</v>
       </c>
@@ -3821,16 +3815,16 @@
       <c r="AH68" s="11"/>
       <c r="AI68" s="12"/>
       <c r="AJ68" s="13"/>
-      <c r="AK68" s="36"/>
-      <c r="AL68" s="36"/>
+      <c r="AK68" s="37"/>
+      <c r="AL68" s="37"/>
       <c r="AQ68" s="4"/>
     </row>
     <row r="69" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="42">
+      <c r="A69" s="32">
         <v>33</v>
       </c>
-      <c r="B69" s="40"/>
-      <c r="C69" s="41"/>
+      <c r="B69" s="34"/>
+      <c r="C69" s="34"/>
       <c r="D69" s="23">
         <v>0.6</v>
       </c>
@@ -3866,13 +3860,13 @@
       <c r="AH69" s="8"/>
       <c r="AI69" s="9"/>
       <c r="AJ69" s="10"/>
-      <c r="AK69" s="39"/>
-      <c r="AL69" s="39"/>
+      <c r="AK69" s="36"/>
+      <c r="AL69" s="36"/>
     </row>
     <row r="70" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="43"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="38"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="35"/>
+      <c r="C70" s="35"/>
       <c r="D70" s="24">
         <v>0.15</v>
       </c>
@@ -3908,16 +3902,16 @@
       <c r="AH70" s="11"/>
       <c r="AI70" s="12"/>
       <c r="AJ70" s="13"/>
-      <c r="AK70" s="36"/>
-      <c r="AL70" s="36"/>
+      <c r="AK70" s="37"/>
+      <c r="AL70" s="37"/>
       <c r="AQ70" s="4"/>
     </row>
     <row r="71" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="42">
+      <c r="A71" s="32">
         <v>34</v>
       </c>
-      <c r="B71" s="40"/>
-      <c r="C71" s="41"/>
+      <c r="B71" s="34"/>
+      <c r="C71" s="34"/>
       <c r="D71" s="23">
         <v>0.6</v>
       </c>
@@ -3953,13 +3947,13 @@
       <c r="AH71" s="8"/>
       <c r="AI71" s="9"/>
       <c r="AJ71" s="10"/>
-      <c r="AK71" s="39"/>
-      <c r="AL71" s="39"/>
+      <c r="AK71" s="36"/>
+      <c r="AL71" s="36"/>
     </row>
     <row r="72" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="43"/>
-      <c r="B72" s="34"/>
-      <c r="C72" s="38"/>
+      <c r="A72" s="33"/>
+      <c r="B72" s="35"/>
+      <c r="C72" s="35"/>
       <c r="D72" s="24">
         <v>0.15</v>
       </c>
@@ -3995,16 +3989,16 @@
       <c r="AH72" s="11"/>
       <c r="AI72" s="12"/>
       <c r="AJ72" s="13"/>
-      <c r="AK72" s="36"/>
-      <c r="AL72" s="36"/>
+      <c r="AK72" s="37"/>
+      <c r="AL72" s="37"/>
       <c r="AQ72" s="4"/>
     </row>
     <row r="73" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="42">
+      <c r="A73" s="32">
         <v>35</v>
       </c>
-      <c r="B73" s="40"/>
-      <c r="C73" s="41"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
       <c r="D73" s="23">
         <v>0.6</v>
       </c>
@@ -4040,13 +4034,13 @@
       <c r="AH73" s="8"/>
       <c r="AI73" s="9"/>
       <c r="AJ73" s="10"/>
-      <c r="AK73" s="39"/>
-      <c r="AL73" s="39"/>
+      <c r="AK73" s="36"/>
+      <c r="AL73" s="36"/>
     </row>
     <row r="74" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="43"/>
-      <c r="B74" s="34"/>
-      <c r="C74" s="38"/>
+      <c r="A74" s="33"/>
+      <c r="B74" s="35"/>
+      <c r="C74" s="35"/>
       <c r="D74" s="24">
         <v>0.15</v>
       </c>
@@ -4082,16 +4076,16 @@
       <c r="AH74" s="11"/>
       <c r="AI74" s="12"/>
       <c r="AJ74" s="13"/>
-      <c r="AK74" s="36"/>
-      <c r="AL74" s="36"/>
+      <c r="AK74" s="37"/>
+      <c r="AL74" s="37"/>
       <c r="AQ74" s="4"/>
     </row>
     <row r="75" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="42">
+      <c r="A75" s="32">
         <v>36</v>
       </c>
-      <c r="B75" s="40"/>
-      <c r="C75" s="41"/>
+      <c r="B75" s="34"/>
+      <c r="C75" s="34"/>
       <c r="D75" s="23">
         <v>0.6</v>
       </c>
@@ -4127,13 +4121,13 @@
       <c r="AH75" s="8"/>
       <c r="AI75" s="9"/>
       <c r="AJ75" s="10"/>
-      <c r="AK75" s="39"/>
-      <c r="AL75" s="39"/>
+      <c r="AK75" s="36"/>
+      <c r="AL75" s="36"/>
     </row>
     <row r="76" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="43"/>
-      <c r="B76" s="34"/>
-      <c r="C76" s="38"/>
+      <c r="A76" s="33"/>
+      <c r="B76" s="35"/>
+      <c r="C76" s="35"/>
       <c r="D76" s="24">
         <v>0.15</v>
       </c>
@@ -4169,16 +4163,16 @@
       <c r="AH76" s="11"/>
       <c r="AI76" s="12"/>
       <c r="AJ76" s="13"/>
-      <c r="AK76" s="36"/>
-      <c r="AL76" s="36"/>
+      <c r="AK76" s="37"/>
+      <c r="AL76" s="37"/>
       <c r="AQ76" s="4"/>
     </row>
     <row r="77" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="42">
+      <c r="A77" s="32">
         <v>37</v>
       </c>
-      <c r="B77" s="40"/>
-      <c r="C77" s="41"/>
+      <c r="B77" s="34"/>
+      <c r="C77" s="34"/>
       <c r="D77" s="23">
         <v>0.6</v>
       </c>
@@ -4214,13 +4208,13 @@
       <c r="AH77" s="8"/>
       <c r="AI77" s="9"/>
       <c r="AJ77" s="10"/>
-      <c r="AK77" s="39"/>
-      <c r="AL77" s="39"/>
+      <c r="AK77" s="36"/>
+      <c r="AL77" s="36"/>
     </row>
     <row r="78" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="43"/>
-      <c r="B78" s="34"/>
-      <c r="C78" s="38"/>
+      <c r="A78" s="33"/>
+      <c r="B78" s="35"/>
+      <c r="C78" s="35"/>
       <c r="D78" s="24">
         <v>0.15</v>
       </c>
@@ -4256,16 +4250,16 @@
       <c r="AH78" s="11"/>
       <c r="AI78" s="12"/>
       <c r="AJ78" s="13"/>
-      <c r="AK78" s="36"/>
-      <c r="AL78" s="36"/>
+      <c r="AK78" s="37"/>
+      <c r="AL78" s="37"/>
       <c r="AQ78" s="4"/>
     </row>
     <row r="79" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="42">
+      <c r="A79" s="32">
         <v>38</v>
       </c>
-      <c r="B79" s="40"/>
-      <c r="C79" s="41"/>
+      <c r="B79" s="34"/>
+      <c r="C79" s="34"/>
       <c r="D79" s="23">
         <v>0.6</v>
       </c>
@@ -4301,13 +4295,13 @@
       <c r="AH79" s="8"/>
       <c r="AI79" s="9"/>
       <c r="AJ79" s="10"/>
-      <c r="AK79" s="39"/>
-      <c r="AL79" s="39"/>
+      <c r="AK79" s="36"/>
+      <c r="AL79" s="36"/>
     </row>
     <row r="80" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="43"/>
-      <c r="B80" s="34"/>
-      <c r="C80" s="38"/>
+      <c r="A80" s="33"/>
+      <c r="B80" s="35"/>
+      <c r="C80" s="35"/>
       <c r="D80" s="24">
         <v>0.15</v>
       </c>
@@ -4343,16 +4337,16 @@
       <c r="AH80" s="11"/>
       <c r="AI80" s="12"/>
       <c r="AJ80" s="13"/>
-      <c r="AK80" s="36"/>
-      <c r="AL80" s="36"/>
+      <c r="AK80" s="37"/>
+      <c r="AL80" s="37"/>
       <c r="AQ80" s="4"/>
     </row>
     <row r="81" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="42">
+      <c r="A81" s="32">
         <v>39</v>
       </c>
-      <c r="B81" s="40"/>
-      <c r="C81" s="41"/>
+      <c r="B81" s="34"/>
+      <c r="C81" s="34"/>
       <c r="D81" s="23">
         <v>0.6</v>
       </c>
@@ -4388,13 +4382,13 @@
       <c r="AH81" s="8"/>
       <c r="AI81" s="9"/>
       <c r="AJ81" s="10"/>
-      <c r="AK81" s="39"/>
-      <c r="AL81" s="39"/>
+      <c r="AK81" s="36"/>
+      <c r="AL81" s="36"/>
     </row>
     <row r="82" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="43"/>
-      <c r="B82" s="34"/>
-      <c r="C82" s="38"/>
+      <c r="A82" s="33"/>
+      <c r="B82" s="35"/>
+      <c r="C82" s="35"/>
       <c r="D82" s="24">
         <v>0.15</v>
       </c>
@@ -4430,16 +4424,16 @@
       <c r="AH82" s="11"/>
       <c r="AI82" s="12"/>
       <c r="AJ82" s="13"/>
-      <c r="AK82" s="36"/>
-      <c r="AL82" s="36"/>
+      <c r="AK82" s="37"/>
+      <c r="AL82" s="37"/>
       <c r="AQ82" s="4"/>
     </row>
     <row r="83" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="42">
+      <c r="A83" s="32">
         <v>40</v>
       </c>
-      <c r="B83" s="40"/>
-      <c r="C83" s="41"/>
+      <c r="B83" s="34"/>
+      <c r="C83" s="34"/>
       <c r="D83" s="23">
         <v>0.6</v>
       </c>
@@ -4475,13 +4469,13 @@
       <c r="AH83" s="8"/>
       <c r="AI83" s="9"/>
       <c r="AJ83" s="10"/>
-      <c r="AK83" s="39"/>
-      <c r="AL83" s="39"/>
+      <c r="AK83" s="36"/>
+      <c r="AL83" s="36"/>
     </row>
     <row r="84" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="43"/>
-      <c r="B84" s="34"/>
-      <c r="C84" s="38"/>
+      <c r="A84" s="33"/>
+      <c r="B84" s="35"/>
+      <c r="C84" s="35"/>
       <c r="D84" s="24">
         <v>0.15</v>
       </c>
@@ -4517,16 +4511,16 @@
       <c r="AH84" s="11"/>
       <c r="AI84" s="12"/>
       <c r="AJ84" s="13"/>
-      <c r="AK84" s="36"/>
-      <c r="AL84" s="36"/>
+      <c r="AK84" s="37"/>
+      <c r="AL84" s="37"/>
       <c r="AQ84" s="4"/>
     </row>
     <row r="85" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="42">
+      <c r="A85" s="32">
         <v>41</v>
       </c>
-      <c r="B85" s="40"/>
-      <c r="C85" s="41"/>
+      <c r="B85" s="34"/>
+      <c r="C85" s="34"/>
       <c r="D85" s="23">
         <v>0.6</v>
       </c>
@@ -4562,13 +4556,13 @@
       <c r="AH85" s="8"/>
       <c r="AI85" s="9"/>
       <c r="AJ85" s="10"/>
-      <c r="AK85" s="39"/>
-      <c r="AL85" s="39"/>
+      <c r="AK85" s="36"/>
+      <c r="AL85" s="36"/>
     </row>
     <row r="86" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="43"/>
-      <c r="B86" s="34"/>
-      <c r="C86" s="38"/>
+      <c r="A86" s="33"/>
+      <c r="B86" s="35"/>
+      <c r="C86" s="35"/>
       <c r="D86" s="24">
         <v>0.15</v>
       </c>
@@ -4604,16 +4598,16 @@
       <c r="AH86" s="11"/>
       <c r="AI86" s="12"/>
       <c r="AJ86" s="13"/>
-      <c r="AK86" s="36"/>
-      <c r="AL86" s="36"/>
+      <c r="AK86" s="37"/>
+      <c r="AL86" s="37"/>
       <c r="AQ86" s="4"/>
     </row>
     <row r="87" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="42">
+      <c r="A87" s="32">
         <v>42</v>
       </c>
-      <c r="B87" s="40"/>
-      <c r="C87" s="41"/>
+      <c r="B87" s="34"/>
+      <c r="C87" s="34"/>
       <c r="D87" s="23">
         <v>0.6</v>
       </c>
@@ -4649,13 +4643,13 @@
       <c r="AH87" s="8"/>
       <c r="AI87" s="9"/>
       <c r="AJ87" s="10"/>
-      <c r="AK87" s="39"/>
-      <c r="AL87" s="39"/>
+      <c r="AK87" s="36"/>
+      <c r="AL87" s="36"/>
     </row>
     <row r="88" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="43"/>
-      <c r="B88" s="34"/>
-      <c r="C88" s="38"/>
+      <c r="A88" s="33"/>
+      <c r="B88" s="35"/>
+      <c r="C88" s="35"/>
       <c r="D88" s="24">
         <v>0.15</v>
       </c>
@@ -4691,16 +4685,16 @@
       <c r="AH88" s="11"/>
       <c r="AI88" s="12"/>
       <c r="AJ88" s="13"/>
-      <c r="AK88" s="36"/>
-      <c r="AL88" s="36"/>
+      <c r="AK88" s="37"/>
+      <c r="AL88" s="37"/>
       <c r="AQ88" s="4"/>
     </row>
     <row r="89" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="42">
+      <c r="A89" s="32">
         <v>43</v>
       </c>
-      <c r="B89" s="40"/>
-      <c r="C89" s="41"/>
+      <c r="B89" s="34"/>
+      <c r="C89" s="34"/>
       <c r="D89" s="23">
         <v>0.6</v>
       </c>
@@ -4736,13 +4730,13 @@
       <c r="AH89" s="8"/>
       <c r="AI89" s="9"/>
       <c r="AJ89" s="10"/>
-      <c r="AK89" s="39"/>
-      <c r="AL89" s="39"/>
+      <c r="AK89" s="36"/>
+      <c r="AL89" s="36"/>
     </row>
     <row r="90" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="43"/>
-      <c r="B90" s="34"/>
-      <c r="C90" s="38"/>
+      <c r="A90" s="33"/>
+      <c r="B90" s="35"/>
+      <c r="C90" s="35"/>
       <c r="D90" s="24">
         <v>0.15</v>
       </c>
@@ -4778,16 +4772,16 @@
       <c r="AH90" s="11"/>
       <c r="AI90" s="12"/>
       <c r="AJ90" s="13"/>
-      <c r="AK90" s="36"/>
-      <c r="AL90" s="36"/>
+      <c r="AK90" s="37"/>
+      <c r="AL90" s="37"/>
       <c r="AQ90" s="4"/>
     </row>
     <row r="91" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="42">
+      <c r="A91" s="32">
         <v>44</v>
       </c>
-      <c r="B91" s="40"/>
-      <c r="C91" s="41"/>
+      <c r="B91" s="34"/>
+      <c r="C91" s="34"/>
       <c r="D91" s="23">
         <v>0.6</v>
       </c>
@@ -4823,13 +4817,13 @@
       <c r="AH91" s="8"/>
       <c r="AI91" s="9"/>
       <c r="AJ91" s="10"/>
-      <c r="AK91" s="39"/>
-      <c r="AL91" s="39"/>
+      <c r="AK91" s="36"/>
+      <c r="AL91" s="36"/>
     </row>
     <row r="92" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="43"/>
-      <c r="B92" s="34"/>
-      <c r="C92" s="38"/>
+      <c r="A92" s="33"/>
+      <c r="B92" s="35"/>
+      <c r="C92" s="35"/>
       <c r="D92" s="24">
         <v>0.15</v>
       </c>
@@ -4865,16 +4859,16 @@
       <c r="AH92" s="11"/>
       <c r="AI92" s="12"/>
       <c r="AJ92" s="13"/>
-      <c r="AK92" s="36"/>
-      <c r="AL92" s="36"/>
+      <c r="AK92" s="37"/>
+      <c r="AL92" s="37"/>
       <c r="AQ92" s="4"/>
     </row>
     <row r="93" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="42">
+      <c r="A93" s="32">
         <v>45</v>
       </c>
-      <c r="B93" s="40"/>
-      <c r="C93" s="41"/>
+      <c r="B93" s="34"/>
+      <c r="C93" s="34"/>
       <c r="D93" s="23">
         <v>0.6</v>
       </c>
@@ -4910,13 +4904,13 @@
       <c r="AH93" s="8"/>
       <c r="AI93" s="9"/>
       <c r="AJ93" s="10"/>
-      <c r="AK93" s="39"/>
-      <c r="AL93" s="39"/>
+      <c r="AK93" s="36"/>
+      <c r="AL93" s="36"/>
     </row>
     <row r="94" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="43"/>
-      <c r="B94" s="34"/>
-      <c r="C94" s="38"/>
+      <c r="A94" s="33"/>
+      <c r="B94" s="35"/>
+      <c r="C94" s="35"/>
       <c r="D94" s="24">
         <v>0.15</v>
       </c>
@@ -4952,16 +4946,16 @@
       <c r="AH94" s="11"/>
       <c r="AI94" s="12"/>
       <c r="AJ94" s="13"/>
-      <c r="AK94" s="36"/>
-      <c r="AL94" s="36"/>
+      <c r="AK94" s="37"/>
+      <c r="AL94" s="37"/>
       <c r="AQ94" s="4"/>
     </row>
     <row r="95" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="42">
+      <c r="A95" s="32">
         <v>46</v>
       </c>
-      <c r="B95" s="40"/>
-      <c r="C95" s="41"/>
+      <c r="B95" s="34"/>
+      <c r="C95" s="34"/>
       <c r="D95" s="23">
         <v>0.6</v>
       </c>
@@ -4997,13 +4991,13 @@
       <c r="AH95" s="8"/>
       <c r="AI95" s="9"/>
       <c r="AJ95" s="10"/>
-      <c r="AK95" s="39"/>
-      <c r="AL95" s="39"/>
+      <c r="AK95" s="36"/>
+      <c r="AL95" s="36"/>
     </row>
     <row r="96" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="43"/>
-      <c r="B96" s="34"/>
-      <c r="C96" s="38"/>
+      <c r="A96" s="33"/>
+      <c r="B96" s="35"/>
+      <c r="C96" s="35"/>
       <c r="D96" s="24">
         <v>0.15</v>
       </c>
@@ -5039,16 +5033,16 @@
       <c r="AH96" s="11"/>
       <c r="AI96" s="12"/>
       <c r="AJ96" s="13"/>
-      <c r="AK96" s="36"/>
-      <c r="AL96" s="36"/>
+      <c r="AK96" s="37"/>
+      <c r="AL96" s="37"/>
       <c r="AQ96" s="4"/>
     </row>
     <row r="97" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="42">
+      <c r="A97" s="32">
         <v>47</v>
       </c>
-      <c r="B97" s="40"/>
-      <c r="C97" s="41"/>
+      <c r="B97" s="34"/>
+      <c r="C97" s="34"/>
       <c r="D97" s="23">
         <v>0.6</v>
       </c>
@@ -5084,13 +5078,13 @@
       <c r="AH97" s="8"/>
       <c r="AI97" s="9"/>
       <c r="AJ97" s="10"/>
-      <c r="AK97" s="39"/>
-      <c r="AL97" s="39"/>
+      <c r="AK97" s="36"/>
+      <c r="AL97" s="36"/>
     </row>
     <row r="98" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="43"/>
-      <c r="B98" s="34"/>
-      <c r="C98" s="38"/>
+      <c r="A98" s="33"/>
+      <c r="B98" s="35"/>
+      <c r="C98" s="35"/>
       <c r="D98" s="24">
         <v>0.15</v>
       </c>
@@ -5126,16 +5120,16 @@
       <c r="AH98" s="11"/>
       <c r="AI98" s="12"/>
       <c r="AJ98" s="13"/>
-      <c r="AK98" s="36"/>
-      <c r="AL98" s="36"/>
+      <c r="AK98" s="37"/>
+      <c r="AL98" s="37"/>
       <c r="AQ98" s="4"/>
     </row>
     <row r="99" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="42">
+      <c r="A99" s="32">
         <v>48</v>
       </c>
-      <c r="B99" s="40"/>
-      <c r="C99" s="41"/>
+      <c r="B99" s="34"/>
+      <c r="C99" s="34"/>
       <c r="D99" s="23">
         <v>0.6</v>
       </c>
@@ -5171,13 +5165,13 @@
       <c r="AH99" s="8"/>
       <c r="AI99" s="9"/>
       <c r="AJ99" s="10"/>
-      <c r="AK99" s="39"/>
-      <c r="AL99" s="39"/>
+      <c r="AK99" s="36"/>
+      <c r="AL99" s="36"/>
     </row>
     <row r="100" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="43"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="38"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="35"/>
+      <c r="C100" s="35"/>
       <c r="D100" s="24">
         <v>0.15</v>
       </c>
@@ -5213,16 +5207,16 @@
       <c r="AH100" s="11"/>
       <c r="AI100" s="12"/>
       <c r="AJ100" s="13"/>
-      <c r="AK100" s="36"/>
-      <c r="AL100" s="36"/>
+      <c r="AK100" s="37"/>
+      <c r="AL100" s="37"/>
       <c r="AQ100" s="4"/>
     </row>
     <row r="101" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="42">
+      <c r="A101" s="32">
         <v>49</v>
       </c>
-      <c r="B101" s="40"/>
-      <c r="C101" s="41"/>
+      <c r="B101" s="34"/>
+      <c r="C101" s="34"/>
       <c r="D101" s="23">
         <v>0.6</v>
       </c>
@@ -5258,13 +5252,13 @@
       <c r="AH101" s="8"/>
       <c r="AI101" s="9"/>
       <c r="AJ101" s="10"/>
-      <c r="AK101" s="39"/>
-      <c r="AL101" s="39"/>
+      <c r="AK101" s="36"/>
+      <c r="AL101" s="36"/>
     </row>
     <row r="102" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="43"/>
-      <c r="B102" s="34"/>
-      <c r="C102" s="38"/>
+      <c r="A102" s="33"/>
+      <c r="B102" s="35"/>
+      <c r="C102" s="35"/>
       <c r="D102" s="24">
         <v>0.15</v>
       </c>
@@ -5300,16 +5294,16 @@
       <c r="AH102" s="11"/>
       <c r="AI102" s="12"/>
       <c r="AJ102" s="13"/>
-      <c r="AK102" s="36"/>
-      <c r="AL102" s="36"/>
+      <c r="AK102" s="37"/>
+      <c r="AL102" s="37"/>
       <c r="AQ102" s="4"/>
     </row>
     <row r="103" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="42">
+      <c r="A103" s="32">
         <v>50</v>
       </c>
-      <c r="B103" s="40"/>
-      <c r="C103" s="41"/>
+      <c r="B103" s="34"/>
+      <c r="C103" s="34"/>
       <c r="D103" s="23">
         <v>0.6</v>
       </c>
@@ -5345,13 +5339,13 @@
       <c r="AH103" s="8"/>
       <c r="AI103" s="9"/>
       <c r="AJ103" s="10"/>
-      <c r="AK103" s="39"/>
-      <c r="AL103" s="39"/>
+      <c r="AK103" s="36"/>
+      <c r="AL103" s="36"/>
     </row>
     <row r="104" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="43"/>
-      <c r="B104" s="34"/>
-      <c r="C104" s="38"/>
+      <c r="A104" s="33"/>
+      <c r="B104" s="35"/>
+      <c r="C104" s="35"/>
       <c r="D104" s="24">
         <v>0.15</v>
       </c>
@@ -5387,16 +5381,16 @@
       <c r="AH104" s="11"/>
       <c r="AI104" s="12"/>
       <c r="AJ104" s="13"/>
-      <c r="AK104" s="36"/>
-      <c r="AL104" s="36"/>
+      <c r="AK104" s="37"/>
+      <c r="AL104" s="37"/>
       <c r="AQ104" s="4"/>
     </row>
     <row r="105" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="42">
+      <c r="A105" s="32">
         <v>51</v>
       </c>
-      <c r="B105" s="33"/>
-      <c r="C105" s="37"/>
+      <c r="B105" s="38"/>
+      <c r="C105" s="38"/>
       <c r="D105" s="23">
         <v>0.6</v>
       </c>
@@ -5432,13 +5426,13 @@
       <c r="AH105" s="8"/>
       <c r="AI105" s="9"/>
       <c r="AJ105" s="10"/>
-      <c r="AK105" s="35"/>
-      <c r="AL105" s="35"/>
+      <c r="AK105" s="39"/>
+      <c r="AL105" s="39"/>
     </row>
     <row r="106" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="43"/>
-      <c r="B106" s="34"/>
-      <c r="C106" s="38"/>
+      <c r="A106" s="33"/>
+      <c r="B106" s="35"/>
+      <c r="C106" s="35"/>
       <c r="D106" s="24">
         <v>0.15</v>
       </c>
@@ -5474,16 +5468,16 @@
       <c r="AH106" s="11"/>
       <c r="AI106" s="12"/>
       <c r="AJ106" s="13"/>
-      <c r="AK106" s="36"/>
-      <c r="AL106" s="36"/>
+      <c r="AK106" s="37"/>
+      <c r="AL106" s="37"/>
       <c r="AQ106" s="4"/>
     </row>
     <row r="107" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="42">
+      <c r="A107" s="32">
         <v>52</v>
       </c>
-      <c r="B107" s="33"/>
-      <c r="C107" s="37"/>
+      <c r="B107" s="38"/>
+      <c r="C107" s="38"/>
       <c r="D107" s="23">
         <v>0.6</v>
       </c>
@@ -5519,13 +5513,13 @@
       <c r="AH107" s="8"/>
       <c r="AI107" s="9"/>
       <c r="AJ107" s="10"/>
-      <c r="AK107" s="35"/>
-      <c r="AL107" s="35"/>
+      <c r="AK107" s="39"/>
+      <c r="AL107" s="39"/>
     </row>
     <row r="108" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="43"/>
-      <c r="B108" s="34"/>
-      <c r="C108" s="38"/>
+      <c r="A108" s="33"/>
+      <c r="B108" s="35"/>
+      <c r="C108" s="35"/>
       <c r="D108" s="24">
         <v>0.15</v>
       </c>
@@ -5561,16 +5555,16 @@
       <c r="AH108" s="11"/>
       <c r="AI108" s="12"/>
       <c r="AJ108" s="13"/>
-      <c r="AK108" s="36"/>
-      <c r="AL108" s="36"/>
+      <c r="AK108" s="37"/>
+      <c r="AL108" s="37"/>
       <c r="AQ108" s="4"/>
     </row>
     <row r="109" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="42">
+      <c r="A109" s="32">
         <v>53</v>
       </c>
-      <c r="B109" s="40"/>
-      <c r="C109" s="41"/>
+      <c r="B109" s="34"/>
+      <c r="C109" s="34"/>
       <c r="D109" s="23">
         <v>0.6</v>
       </c>
@@ -5606,13 +5600,13 @@
       <c r="AH109" s="8"/>
       <c r="AI109" s="9"/>
       <c r="AJ109" s="10"/>
-      <c r="AK109" s="39"/>
-      <c r="AL109" s="39"/>
+      <c r="AK109" s="36"/>
+      <c r="AL109" s="36"/>
     </row>
     <row r="110" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="43"/>
-      <c r="B110" s="34"/>
-      <c r="C110" s="38"/>
+      <c r="A110" s="33"/>
+      <c r="B110" s="35"/>
+      <c r="C110" s="35"/>
       <c r="D110" s="24">
         <v>0.15</v>
       </c>
@@ -5648,16 +5642,16 @@
       <c r="AH110" s="11"/>
       <c r="AI110" s="12"/>
       <c r="AJ110" s="13"/>
-      <c r="AK110" s="36"/>
-      <c r="AL110" s="36"/>
+      <c r="AK110" s="37"/>
+      <c r="AL110" s="37"/>
       <c r="AQ110" s="4"/>
     </row>
     <row r="111" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="42">
+      <c r="A111" s="32">
         <v>54</v>
       </c>
-      <c r="B111" s="40"/>
-      <c r="C111" s="41"/>
+      <c r="B111" s="34"/>
+      <c r="C111" s="34"/>
       <c r="D111" s="23">
         <v>0.6</v>
       </c>
@@ -5693,13 +5687,13 @@
       <c r="AH111" s="8"/>
       <c r="AI111" s="9"/>
       <c r="AJ111" s="10"/>
-      <c r="AK111" s="39"/>
-      <c r="AL111" s="39"/>
+      <c r="AK111" s="36"/>
+      <c r="AL111" s="36"/>
     </row>
     <row r="112" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="43"/>
-      <c r="B112" s="34"/>
-      <c r="C112" s="38"/>
+      <c r="A112" s="33"/>
+      <c r="B112" s="35"/>
+      <c r="C112" s="35"/>
       <c r="D112" s="24">
         <v>0.15</v>
       </c>
@@ -5735,16 +5729,16 @@
       <c r="AH112" s="11"/>
       <c r="AI112" s="12"/>
       <c r="AJ112" s="13"/>
-      <c r="AK112" s="36"/>
-      <c r="AL112" s="36"/>
+      <c r="AK112" s="37"/>
+      <c r="AL112" s="37"/>
       <c r="AQ112" s="4"/>
     </row>
     <row r="113" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="42">
+      <c r="A113" s="32">
         <v>55</v>
       </c>
-      <c r="B113" s="40"/>
-      <c r="C113" s="41"/>
+      <c r="B113" s="34"/>
+      <c r="C113" s="34"/>
       <c r="D113" s="23">
         <v>0.6</v>
       </c>
@@ -5780,13 +5774,13 @@
       <c r="AH113" s="8"/>
       <c r="AI113" s="9"/>
       <c r="AJ113" s="10"/>
-      <c r="AK113" s="39"/>
-      <c r="AL113" s="39"/>
+      <c r="AK113" s="36"/>
+      <c r="AL113" s="36"/>
     </row>
     <row r="114" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="43"/>
-      <c r="B114" s="34"/>
-      <c r="C114" s="38"/>
+      <c r="A114" s="33"/>
+      <c r="B114" s="35"/>
+      <c r="C114" s="35"/>
       <c r="D114" s="24">
         <v>0.15</v>
       </c>
@@ -5822,16 +5816,16 @@
       <c r="AH114" s="11"/>
       <c r="AI114" s="12"/>
       <c r="AJ114" s="13"/>
-      <c r="AK114" s="36"/>
-      <c r="AL114" s="36"/>
+      <c r="AK114" s="37"/>
+      <c r="AL114" s="37"/>
       <c r="AQ114" s="4"/>
     </row>
     <row r="115" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="42">
+      <c r="A115" s="32">
         <v>56</v>
       </c>
-      <c r="B115" s="40"/>
-      <c r="C115" s="41"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="34"/>
       <c r="D115" s="23">
         <v>0.6</v>
       </c>
@@ -5867,13 +5861,13 @@
       <c r="AH115" s="8"/>
       <c r="AI115" s="9"/>
       <c r="AJ115" s="10"/>
-      <c r="AK115" s="39"/>
-      <c r="AL115" s="39"/>
+      <c r="AK115" s="36"/>
+      <c r="AL115" s="36"/>
     </row>
     <row r="116" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="43"/>
-      <c r="B116" s="34"/>
-      <c r="C116" s="38"/>
+      <c r="A116" s="33"/>
+      <c r="B116" s="35"/>
+      <c r="C116" s="35"/>
       <c r="D116" s="24">
         <v>0.15</v>
       </c>
@@ -5909,16 +5903,16 @@
       <c r="AH116" s="11"/>
       <c r="AI116" s="12"/>
       <c r="AJ116" s="13"/>
-      <c r="AK116" s="36"/>
-      <c r="AL116" s="36"/>
+      <c r="AK116" s="37"/>
+      <c r="AL116" s="37"/>
       <c r="AQ116" s="4"/>
     </row>
     <row r="117" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="42">
+      <c r="A117" s="32">
         <v>57</v>
       </c>
-      <c r="B117" s="40"/>
-      <c r="C117" s="41"/>
+      <c r="B117" s="34"/>
+      <c r="C117" s="34"/>
       <c r="D117" s="23">
         <v>0.6</v>
       </c>
@@ -5954,13 +5948,13 @@
       <c r="AH117" s="8"/>
       <c r="AI117" s="9"/>
       <c r="AJ117" s="10"/>
-      <c r="AK117" s="39"/>
-      <c r="AL117" s="39"/>
+      <c r="AK117" s="36"/>
+      <c r="AL117" s="36"/>
     </row>
     <row r="118" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="43"/>
-      <c r="B118" s="34"/>
-      <c r="C118" s="38"/>
+      <c r="A118" s="33"/>
+      <c r="B118" s="35"/>
+      <c r="C118" s="35"/>
       <c r="D118" s="24">
         <v>0.15</v>
       </c>
@@ -5996,16 +5990,16 @@
       <c r="AH118" s="11"/>
       <c r="AI118" s="12"/>
       <c r="AJ118" s="13"/>
-      <c r="AK118" s="36"/>
-      <c r="AL118" s="36"/>
+      <c r="AK118" s="37"/>
+      <c r="AL118" s="37"/>
       <c r="AQ118" s="4"/>
     </row>
     <row r="119" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="42">
+      <c r="A119" s="32">
         <v>58</v>
       </c>
-      <c r="B119" s="40"/>
-      <c r="C119" s="41"/>
+      <c r="B119" s="34"/>
+      <c r="C119" s="34"/>
       <c r="D119" s="23">
         <v>0.6</v>
       </c>
@@ -6041,13 +6035,13 @@
       <c r="AH119" s="8"/>
       <c r="AI119" s="9"/>
       <c r="AJ119" s="10"/>
-      <c r="AK119" s="39"/>
-      <c r="AL119" s="39"/>
+      <c r="AK119" s="36"/>
+      <c r="AL119" s="36"/>
     </row>
     <row r="120" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="43"/>
-      <c r="B120" s="34"/>
-      <c r="C120" s="38"/>
+      <c r="A120" s="33"/>
+      <c r="B120" s="35"/>
+      <c r="C120" s="35"/>
       <c r="D120" s="24">
         <v>0.15</v>
       </c>
@@ -6083,16 +6077,16 @@
       <c r="AH120" s="11"/>
       <c r="AI120" s="12"/>
       <c r="AJ120" s="13"/>
-      <c r="AK120" s="36"/>
-      <c r="AL120" s="36"/>
+      <c r="AK120" s="37"/>
+      <c r="AL120" s="37"/>
       <c r="AQ120" s="4"/>
     </row>
     <row r="121" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="42">
+      <c r="A121" s="32">
         <v>59</v>
       </c>
-      <c r="B121" s="40"/>
-      <c r="C121" s="41"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
       <c r="D121" s="23">
         <v>0.6</v>
       </c>
@@ -6128,13 +6122,13 @@
       <c r="AH121" s="8"/>
       <c r="AI121" s="9"/>
       <c r="AJ121" s="10"/>
-      <c r="AK121" s="39"/>
-      <c r="AL121" s="39"/>
+      <c r="AK121" s="36"/>
+      <c r="AL121" s="36"/>
     </row>
     <row r="122" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="43"/>
-      <c r="B122" s="34"/>
-      <c r="C122" s="38"/>
+      <c r="A122" s="33"/>
+      <c r="B122" s="35"/>
+      <c r="C122" s="35"/>
       <c r="D122" s="24">
         <v>0.15</v>
       </c>
@@ -6170,16 +6164,16 @@
       <c r="AH122" s="11"/>
       <c r="AI122" s="12"/>
       <c r="AJ122" s="13"/>
-      <c r="AK122" s="36"/>
-      <c r="AL122" s="36"/>
+      <c r="AK122" s="37"/>
+      <c r="AL122" s="37"/>
       <c r="AQ122" s="4"/>
     </row>
     <row r="123" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="42">
+      <c r="A123" s="32">
         <v>60</v>
       </c>
-      <c r="B123" s="40"/>
-      <c r="C123" s="41"/>
+      <c r="B123" s="34"/>
+      <c r="C123" s="34"/>
       <c r="D123" s="23">
         <v>0.6</v>
       </c>
@@ -6215,13 +6209,13 @@
       <c r="AH123" s="8"/>
       <c r="AI123" s="9"/>
       <c r="AJ123" s="10"/>
-      <c r="AK123" s="39"/>
-      <c r="AL123" s="39"/>
+      <c r="AK123" s="36"/>
+      <c r="AL123" s="36"/>
     </row>
     <row r="124" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="43"/>
-      <c r="B124" s="34"/>
-      <c r="C124" s="38"/>
+      <c r="A124" s="33"/>
+      <c r="B124" s="35"/>
+      <c r="C124" s="35"/>
       <c r="D124" s="24">
         <v>0.15</v>
       </c>
@@ -6257,16 +6251,16 @@
       <c r="AH124" s="11"/>
       <c r="AI124" s="12"/>
       <c r="AJ124" s="13"/>
-      <c r="AK124" s="36"/>
-      <c r="AL124" s="36"/>
+      <c r="AK124" s="37"/>
+      <c r="AL124" s="37"/>
       <c r="AQ124" s="4"/>
     </row>
     <row r="125" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="42">
+      <c r="A125" s="32">
         <v>61</v>
       </c>
-      <c r="B125" s="40"/>
-      <c r="C125" s="41"/>
+      <c r="B125" s="34"/>
+      <c r="C125" s="34"/>
       <c r="D125" s="23">
         <v>0.6</v>
       </c>
@@ -6302,13 +6296,13 @@
       <c r="AH125" s="8"/>
       <c r="AI125" s="9"/>
       <c r="AJ125" s="10"/>
-      <c r="AK125" s="39"/>
-      <c r="AL125" s="39"/>
+      <c r="AK125" s="36"/>
+      <c r="AL125" s="36"/>
     </row>
     <row r="126" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="43"/>
-      <c r="B126" s="34"/>
-      <c r="C126" s="38"/>
+      <c r="A126" s="33"/>
+      <c r="B126" s="35"/>
+      <c r="C126" s="35"/>
       <c r="D126" s="24">
         <v>0.15</v>
       </c>
@@ -6344,16 +6338,16 @@
       <c r="AH126" s="11"/>
       <c r="AI126" s="12"/>
       <c r="AJ126" s="13"/>
-      <c r="AK126" s="36"/>
-      <c r="AL126" s="36"/>
+      <c r="AK126" s="37"/>
+      <c r="AL126" s="37"/>
       <c r="AQ126" s="4"/>
     </row>
     <row r="127" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="42">
+      <c r="A127" s="32">
         <v>62</v>
       </c>
-      <c r="B127" s="40"/>
-      <c r="C127" s="41"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="34"/>
       <c r="D127" s="23">
         <v>0.6</v>
       </c>
@@ -6389,13 +6383,13 @@
       <c r="AH127" s="8"/>
       <c r="AI127" s="9"/>
       <c r="AJ127" s="10"/>
-      <c r="AK127" s="39"/>
-      <c r="AL127" s="39"/>
+      <c r="AK127" s="36"/>
+      <c r="AL127" s="36"/>
     </row>
     <row r="128" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="43"/>
-      <c r="B128" s="34"/>
-      <c r="C128" s="38"/>
+      <c r="A128" s="33"/>
+      <c r="B128" s="35"/>
+      <c r="C128" s="35"/>
       <c r="D128" s="24">
         <v>0.15</v>
       </c>
@@ -6431,16 +6425,16 @@
       <c r="AH128" s="11"/>
       <c r="AI128" s="12"/>
       <c r="AJ128" s="13"/>
-      <c r="AK128" s="36"/>
-      <c r="AL128" s="36"/>
+      <c r="AK128" s="37"/>
+      <c r="AL128" s="37"/>
       <c r="AQ128" s="4"/>
     </row>
     <row r="129" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="42">
+      <c r="A129" s="32">
         <v>63</v>
       </c>
-      <c r="B129" s="40"/>
-      <c r="C129" s="41"/>
+      <c r="B129" s="34"/>
+      <c r="C129" s="34"/>
       <c r="D129" s="23">
         <v>0.6</v>
       </c>
@@ -6476,13 +6470,13 @@
       <c r="AH129" s="8"/>
       <c r="AI129" s="9"/>
       <c r="AJ129" s="10"/>
-      <c r="AK129" s="39"/>
-      <c r="AL129" s="39"/>
+      <c r="AK129" s="36"/>
+      <c r="AL129" s="36"/>
     </row>
     <row r="130" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="43"/>
-      <c r="B130" s="34"/>
-      <c r="C130" s="38"/>
+      <c r="A130" s="33"/>
+      <c r="B130" s="35"/>
+      <c r="C130" s="35"/>
       <c r="D130" s="24">
         <v>0.15</v>
       </c>
@@ -6518,16 +6512,16 @@
       <c r="AH130" s="11"/>
       <c r="AI130" s="12"/>
       <c r="AJ130" s="13"/>
-      <c r="AK130" s="36"/>
-      <c r="AL130" s="36"/>
+      <c r="AK130" s="37"/>
+      <c r="AL130" s="37"/>
       <c r="AQ130" s="4"/>
     </row>
     <row r="131" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="42">
+      <c r="A131" s="32">
         <v>64</v>
       </c>
-      <c r="B131" s="40"/>
-      <c r="C131" s="41"/>
+      <c r="B131" s="34"/>
+      <c r="C131" s="34"/>
       <c r="D131" s="23">
         <v>0.6</v>
       </c>
@@ -6563,13 +6557,13 @@
       <c r="AH131" s="8"/>
       <c r="AI131" s="9"/>
       <c r="AJ131" s="10"/>
-      <c r="AK131" s="39"/>
-      <c r="AL131" s="39"/>
+      <c r="AK131" s="36"/>
+      <c r="AL131" s="36"/>
     </row>
     <row r="132" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="43"/>
-      <c r="B132" s="34"/>
-      <c r="C132" s="38"/>
+      <c r="A132" s="33"/>
+      <c r="B132" s="35"/>
+      <c r="C132" s="35"/>
       <c r="D132" s="24">
         <v>0.15</v>
       </c>
@@ -6605,16 +6599,16 @@
       <c r="AH132" s="11"/>
       <c r="AI132" s="12"/>
       <c r="AJ132" s="13"/>
-      <c r="AK132" s="36"/>
-      <c r="AL132" s="36"/>
+      <c r="AK132" s="37"/>
+      <c r="AL132" s="37"/>
       <c r="AQ132" s="4"/>
     </row>
     <row r="133" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="42">
+      <c r="A133" s="32">
         <v>65</v>
       </c>
-      <c r="B133" s="40"/>
-      <c r="C133" s="41"/>
+      <c r="B133" s="34"/>
+      <c r="C133" s="34"/>
       <c r="D133" s="23">
         <v>0.6</v>
       </c>
@@ -6650,13 +6644,13 @@
       <c r="AH133" s="8"/>
       <c r="AI133" s="9"/>
       <c r="AJ133" s="10"/>
-      <c r="AK133" s="39"/>
-      <c r="AL133" s="39"/>
+      <c r="AK133" s="36"/>
+      <c r="AL133" s="36"/>
     </row>
     <row r="134" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="43"/>
-      <c r="B134" s="34"/>
-      <c r="C134" s="38"/>
+      <c r="A134" s="33"/>
+      <c r="B134" s="35"/>
+      <c r="C134" s="35"/>
       <c r="D134" s="24">
         <v>0.15</v>
       </c>
@@ -6692,16 +6686,16 @@
       <c r="AH134" s="11"/>
       <c r="AI134" s="12"/>
       <c r="AJ134" s="13"/>
-      <c r="AK134" s="36"/>
-      <c r="AL134" s="36"/>
+      <c r="AK134" s="37"/>
+      <c r="AL134" s="37"/>
       <c r="AQ134" s="4"/>
     </row>
     <row r="135" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="42">
+      <c r="A135" s="32">
         <v>66</v>
       </c>
-      <c r="B135" s="40"/>
-      <c r="C135" s="41"/>
+      <c r="B135" s="34"/>
+      <c r="C135" s="34"/>
       <c r="D135" s="23">
         <v>0.6</v>
       </c>
@@ -6737,13 +6731,13 @@
       <c r="AH135" s="8"/>
       <c r="AI135" s="9"/>
       <c r="AJ135" s="10"/>
-      <c r="AK135" s="39"/>
-      <c r="AL135" s="39"/>
+      <c r="AK135" s="36"/>
+      <c r="AL135" s="36"/>
     </row>
     <row r="136" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="43"/>
-      <c r="B136" s="34"/>
-      <c r="C136" s="38"/>
+      <c r="A136" s="33"/>
+      <c r="B136" s="35"/>
+      <c r="C136" s="35"/>
       <c r="D136" s="24">
         <v>0.15</v>
       </c>
@@ -6779,16 +6773,16 @@
       <c r="AH136" s="11"/>
       <c r="AI136" s="12"/>
       <c r="AJ136" s="13"/>
-      <c r="AK136" s="36"/>
-      <c r="AL136" s="36"/>
+      <c r="AK136" s="37"/>
+      <c r="AL136" s="37"/>
       <c r="AQ136" s="4"/>
     </row>
     <row r="137" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="42">
+      <c r="A137" s="32">
         <v>67</v>
       </c>
-      <c r="B137" s="40"/>
-      <c r="C137" s="41"/>
+      <c r="B137" s="34"/>
+      <c r="C137" s="34"/>
       <c r="D137" s="23">
         <v>0.6</v>
       </c>
@@ -6824,13 +6818,13 @@
       <c r="AH137" s="8"/>
       <c r="AI137" s="9"/>
       <c r="AJ137" s="10"/>
-      <c r="AK137" s="39"/>
-      <c r="AL137" s="39"/>
+      <c r="AK137" s="36"/>
+      <c r="AL137" s="36"/>
     </row>
     <row r="138" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="43"/>
-      <c r="B138" s="34"/>
-      <c r="C138" s="38"/>
+      <c r="A138" s="33"/>
+      <c r="B138" s="35"/>
+      <c r="C138" s="35"/>
       <c r="D138" s="24">
         <v>0.15</v>
       </c>
@@ -6866,16 +6860,16 @@
       <c r="AH138" s="11"/>
       <c r="AI138" s="12"/>
       <c r="AJ138" s="13"/>
-      <c r="AK138" s="36"/>
-      <c r="AL138" s="36"/>
+      <c r="AK138" s="37"/>
+      <c r="AL138" s="37"/>
       <c r="AQ138" s="4"/>
     </row>
     <row r="139" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="42">
+      <c r="A139" s="32">
         <v>68</v>
       </c>
-      <c r="B139" s="40"/>
-      <c r="C139" s="41"/>
+      <c r="B139" s="34"/>
+      <c r="C139" s="34"/>
       <c r="D139" s="23">
         <v>0.6</v>
       </c>
@@ -6911,13 +6905,13 @@
       <c r="AH139" s="8"/>
       <c r="AI139" s="9"/>
       <c r="AJ139" s="10"/>
-      <c r="AK139" s="39"/>
-      <c r="AL139" s="39"/>
+      <c r="AK139" s="36"/>
+      <c r="AL139" s="36"/>
     </row>
     <row r="140" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="43"/>
-      <c r="B140" s="34"/>
-      <c r="C140" s="38"/>
+      <c r="A140" s="33"/>
+      <c r="B140" s="35"/>
+      <c r="C140" s="35"/>
       <c r="D140" s="24">
         <v>0.15</v>
       </c>
@@ -6953,16 +6947,16 @@
       <c r="AH140" s="11"/>
       <c r="AI140" s="12"/>
       <c r="AJ140" s="13"/>
-      <c r="AK140" s="36"/>
-      <c r="AL140" s="36"/>
+      <c r="AK140" s="37"/>
+      <c r="AL140" s="37"/>
       <c r="AQ140" s="4"/>
     </row>
     <row r="141" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="42">
+      <c r="A141" s="32">
         <v>69</v>
       </c>
-      <c r="B141" s="40"/>
-      <c r="C141" s="41"/>
+      <c r="B141" s="34"/>
+      <c r="C141" s="34"/>
       <c r="D141" s="23">
         <v>0.6</v>
       </c>
@@ -6998,13 +6992,13 @@
       <c r="AH141" s="8"/>
       <c r="AI141" s="9"/>
       <c r="AJ141" s="10"/>
-      <c r="AK141" s="39"/>
-      <c r="AL141" s="39"/>
+      <c r="AK141" s="36"/>
+      <c r="AL141" s="36"/>
     </row>
     <row r="142" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="43"/>
-      <c r="B142" s="34"/>
-      <c r="C142" s="38"/>
+      <c r="A142" s="33"/>
+      <c r="B142" s="35"/>
+      <c r="C142" s="35"/>
       <c r="D142" s="24">
         <v>0.15</v>
       </c>
@@ -7040,16 +7034,16 @@
       <c r="AH142" s="11"/>
       <c r="AI142" s="12"/>
       <c r="AJ142" s="13"/>
-      <c r="AK142" s="36"/>
-      <c r="AL142" s="36"/>
+      <c r="AK142" s="37"/>
+      <c r="AL142" s="37"/>
       <c r="AQ142" s="4"/>
     </row>
     <row r="143" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="42">
+      <c r="A143" s="32">
         <v>70</v>
       </c>
-      <c r="B143" s="40"/>
-      <c r="C143" s="41"/>
+      <c r="B143" s="34"/>
+      <c r="C143" s="34"/>
       <c r="D143" s="23">
         <v>0.6</v>
       </c>
@@ -7085,13 +7079,13 @@
       <c r="AH143" s="8"/>
       <c r="AI143" s="9"/>
       <c r="AJ143" s="10"/>
-      <c r="AK143" s="39"/>
-      <c r="AL143" s="39"/>
+      <c r="AK143" s="36"/>
+      <c r="AL143" s="36"/>
     </row>
     <row r="144" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="43"/>
-      <c r="B144" s="34"/>
-      <c r="C144" s="38"/>
+      <c r="A144" s="33"/>
+      <c r="B144" s="35"/>
+      <c r="C144" s="35"/>
       <c r="D144" s="24">
         <v>0.15</v>
       </c>
@@ -7127,16 +7121,16 @@
       <c r="AH144" s="11"/>
       <c r="AI144" s="12"/>
       <c r="AJ144" s="13"/>
-      <c r="AK144" s="36"/>
-      <c r="AL144" s="36"/>
+      <c r="AK144" s="37"/>
+      <c r="AL144" s="37"/>
       <c r="AQ144" s="4"/>
     </row>
     <row r="145" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="42">
+      <c r="A145" s="32">
         <v>71</v>
       </c>
-      <c r="B145" s="40"/>
-      <c r="C145" s="41"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="34"/>
       <c r="D145" s="23">
         <v>0.6</v>
       </c>
@@ -7172,13 +7166,13 @@
       <c r="AH145" s="8"/>
       <c r="AI145" s="9"/>
       <c r="AJ145" s="10"/>
-      <c r="AK145" s="39"/>
-      <c r="AL145" s="39"/>
+      <c r="AK145" s="36"/>
+      <c r="AL145" s="36"/>
     </row>
     <row r="146" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="43"/>
-      <c r="B146" s="34"/>
-      <c r="C146" s="38"/>
+      <c r="A146" s="33"/>
+      <c r="B146" s="35"/>
+      <c r="C146" s="35"/>
       <c r="D146" s="24">
         <v>0.15</v>
       </c>
@@ -7214,16 +7208,16 @@
       <c r="AH146" s="11"/>
       <c r="AI146" s="12"/>
       <c r="AJ146" s="13"/>
-      <c r="AK146" s="36"/>
-      <c r="AL146" s="36"/>
+      <c r="AK146" s="37"/>
+      <c r="AL146" s="37"/>
       <c r="AQ146" s="4"/>
     </row>
     <row r="147" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="42">
+      <c r="A147" s="32">
         <v>72</v>
       </c>
-      <c r="B147" s="40"/>
-      <c r="C147" s="41"/>
+      <c r="B147" s="34"/>
+      <c r="C147" s="34"/>
       <c r="D147" s="23">
         <v>0.6</v>
       </c>
@@ -7259,13 +7253,13 @@
       <c r="AH147" s="8"/>
       <c r="AI147" s="9"/>
       <c r="AJ147" s="10"/>
-      <c r="AK147" s="39"/>
-      <c r="AL147" s="39"/>
+      <c r="AK147" s="36"/>
+      <c r="AL147" s="36"/>
     </row>
     <row r="148" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="43"/>
-      <c r="B148" s="34"/>
-      <c r="C148" s="38"/>
+      <c r="A148" s="33"/>
+      <c r="B148" s="35"/>
+      <c r="C148" s="35"/>
       <c r="D148" s="24">
         <v>0.15</v>
       </c>
@@ -7301,16 +7295,16 @@
       <c r="AH148" s="11"/>
       <c r="AI148" s="12"/>
       <c r="AJ148" s="13"/>
-      <c r="AK148" s="36"/>
-      <c r="AL148" s="36"/>
+      <c r="AK148" s="37"/>
+      <c r="AL148" s="37"/>
       <c r="AQ148" s="4"/>
     </row>
     <row r="149" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="42">
+      <c r="A149" s="32">
         <v>73</v>
       </c>
-      <c r="B149" s="40"/>
-      <c r="C149" s="41"/>
+      <c r="B149" s="34"/>
+      <c r="C149" s="34"/>
       <c r="D149" s="23">
         <v>0.6</v>
       </c>
@@ -7346,13 +7340,13 @@
       <c r="AH149" s="8"/>
       <c r="AI149" s="9"/>
       <c r="AJ149" s="10"/>
-      <c r="AK149" s="39"/>
-      <c r="AL149" s="39"/>
+      <c r="AK149" s="36"/>
+      <c r="AL149" s="36"/>
     </row>
     <row r="150" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="43"/>
-      <c r="B150" s="34"/>
-      <c r="C150" s="38"/>
+      <c r="A150" s="33"/>
+      <c r="B150" s="35"/>
+      <c r="C150" s="35"/>
       <c r="D150" s="24">
         <v>0.15</v>
       </c>
@@ -7388,16 +7382,16 @@
       <c r="AH150" s="11"/>
       <c r="AI150" s="12"/>
       <c r="AJ150" s="13"/>
-      <c r="AK150" s="36"/>
-      <c r="AL150" s="36"/>
+      <c r="AK150" s="37"/>
+      <c r="AL150" s="37"/>
       <c r="AQ150" s="4"/>
     </row>
     <row r="151" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="42">
+      <c r="A151" s="32">
         <v>74</v>
       </c>
-      <c r="B151" s="40"/>
-      <c r="C151" s="41"/>
+      <c r="B151" s="34"/>
+      <c r="C151" s="34"/>
       <c r="D151" s="23">
         <v>0.6</v>
       </c>
@@ -7433,13 +7427,13 @@
       <c r="AH151" s="8"/>
       <c r="AI151" s="9"/>
       <c r="AJ151" s="10"/>
-      <c r="AK151" s="39"/>
-      <c r="AL151" s="39"/>
+      <c r="AK151" s="36"/>
+      <c r="AL151" s="36"/>
     </row>
     <row r="152" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="43"/>
-      <c r="B152" s="34"/>
-      <c r="C152" s="38"/>
+      <c r="A152" s="33"/>
+      <c r="B152" s="35"/>
+      <c r="C152" s="35"/>
       <c r="D152" s="24">
         <v>0.15</v>
       </c>
@@ -7475,16 +7469,16 @@
       <c r="AH152" s="11"/>
       <c r="AI152" s="12"/>
       <c r="AJ152" s="13"/>
-      <c r="AK152" s="36"/>
-      <c r="AL152" s="36"/>
+      <c r="AK152" s="37"/>
+      <c r="AL152" s="37"/>
       <c r="AQ152" s="4"/>
     </row>
     <row r="153" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="42">
+      <c r="A153" s="32">
         <v>75</v>
       </c>
-      <c r="B153" s="40"/>
-      <c r="C153" s="41"/>
+      <c r="B153" s="34"/>
+      <c r="C153" s="34"/>
       <c r="D153" s="23">
         <v>0.6</v>
       </c>
@@ -7520,13 +7514,13 @@
       <c r="AH153" s="8"/>
       <c r="AI153" s="9"/>
       <c r="AJ153" s="10"/>
-      <c r="AK153" s="39"/>
-      <c r="AL153" s="39"/>
+      <c r="AK153" s="36"/>
+      <c r="AL153" s="36"/>
     </row>
     <row r="154" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="43"/>
-      <c r="B154" s="34"/>
-      <c r="C154" s="38"/>
+      <c r="A154" s="33"/>
+      <c r="B154" s="35"/>
+      <c r="C154" s="35"/>
       <c r="D154" s="24">
         <v>0.15</v>
       </c>
@@ -7562,16 +7556,16 @@
       <c r="AH154" s="11"/>
       <c r="AI154" s="12"/>
       <c r="AJ154" s="13"/>
-      <c r="AK154" s="36"/>
-      <c r="AL154" s="36"/>
+      <c r="AK154" s="37"/>
+      <c r="AL154" s="37"/>
       <c r="AQ154" s="4"/>
     </row>
     <row r="155" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="42">
+      <c r="A155" s="32">
         <v>76</v>
       </c>
-      <c r="B155" s="40"/>
-      <c r="C155" s="41"/>
+      <c r="B155" s="34"/>
+      <c r="C155" s="34"/>
       <c r="D155" s="23">
         <v>0.6</v>
       </c>
@@ -7607,13 +7601,13 @@
       <c r="AH155" s="8"/>
       <c r="AI155" s="9"/>
       <c r="AJ155" s="10"/>
-      <c r="AK155" s="39"/>
-      <c r="AL155" s="39"/>
+      <c r="AK155" s="36"/>
+      <c r="AL155" s="36"/>
     </row>
     <row r="156" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="43"/>
-      <c r="B156" s="34"/>
-      <c r="C156" s="38"/>
+      <c r="A156" s="33"/>
+      <c r="B156" s="35"/>
+      <c r="C156" s="35"/>
       <c r="D156" s="24">
         <v>0.15</v>
       </c>
@@ -7649,16 +7643,16 @@
       <c r="AH156" s="11"/>
       <c r="AI156" s="12"/>
       <c r="AJ156" s="13"/>
-      <c r="AK156" s="36"/>
-      <c r="AL156" s="36"/>
+      <c r="AK156" s="37"/>
+      <c r="AL156" s="37"/>
       <c r="AQ156" s="4"/>
     </row>
     <row r="157" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="42">
+      <c r="A157" s="32">
         <v>77</v>
       </c>
-      <c r="B157" s="33"/>
-      <c r="C157" s="37"/>
+      <c r="B157" s="38"/>
+      <c r="C157" s="38"/>
       <c r="D157" s="23">
         <v>0.6</v>
       </c>
@@ -7694,13 +7688,13 @@
       <c r="AH157" s="8"/>
       <c r="AI157" s="9"/>
       <c r="AJ157" s="10"/>
-      <c r="AK157" s="35"/>
-      <c r="AL157" s="35"/>
+      <c r="AK157" s="39"/>
+      <c r="AL157" s="39"/>
     </row>
     <row r="158" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="43"/>
-      <c r="B158" s="34"/>
-      <c r="C158" s="38"/>
+      <c r="A158" s="33"/>
+      <c r="B158" s="35"/>
+      <c r="C158" s="35"/>
       <c r="D158" s="24">
         <v>0.15</v>
       </c>
@@ -7736,16 +7730,16 @@
       <c r="AH158" s="11"/>
       <c r="AI158" s="12"/>
       <c r="AJ158" s="13"/>
-      <c r="AK158" s="36"/>
-      <c r="AL158" s="36"/>
+      <c r="AK158" s="37"/>
+      <c r="AL158" s="37"/>
       <c r="AQ158" s="4"/>
     </row>
     <row r="159" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="42">
+      <c r="A159" s="32">
         <v>78</v>
       </c>
-      <c r="B159" s="33"/>
-      <c r="C159" s="37"/>
+      <c r="B159" s="38"/>
+      <c r="C159" s="38"/>
       <c r="D159" s="23">
         <v>0.6</v>
       </c>
@@ -7781,13 +7775,13 @@
       <c r="AH159" s="8"/>
       <c r="AI159" s="9"/>
       <c r="AJ159" s="10"/>
-      <c r="AK159" s="35"/>
-      <c r="AL159" s="35"/>
+      <c r="AK159" s="39"/>
+      <c r="AL159" s="39"/>
     </row>
     <row r="160" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="43"/>
-      <c r="B160" s="34"/>
-      <c r="C160" s="38"/>
+      <c r="A160" s="33"/>
+      <c r="B160" s="35"/>
+      <c r="C160" s="35"/>
       <c r="D160" s="24">
         <v>0.15</v>
       </c>
@@ -7823,25 +7817,25 @@
       <c r="AH160" s="11"/>
       <c r="AI160" s="12"/>
       <c r="AJ160" s="13"/>
-      <c r="AK160" s="36"/>
-      <c r="AL160" s="36"/>
+      <c r="AK160" s="37"/>
+      <c r="AL160" s="37"/>
       <c r="AQ160" s="4"/>
     </row>
     <row r="161" spans="1:43" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C161" s="1"/>
+      <c r="C161" s="42"/>
       <c r="D161" s="25" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="42">
+      <c r="A162" s="32">
         <v>79</v>
       </c>
-      <c r="B162" s="40"/>
-      <c r="C162" s="41"/>
+      <c r="B162" s="34"/>
+      <c r="C162" s="34"/>
       <c r="D162" s="23">
         <v>0.6</v>
       </c>
@@ -7877,13 +7871,13 @@
       <c r="AH162" s="8"/>
       <c r="AI162" s="9"/>
       <c r="AJ162" s="10"/>
-      <c r="AK162" s="39"/>
-      <c r="AL162" s="39"/>
+      <c r="AK162" s="36"/>
+      <c r="AL162" s="36"/>
     </row>
     <row r="163" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="43"/>
-      <c r="B163" s="34"/>
-      <c r="C163" s="38"/>
+      <c r="A163" s="33"/>
+      <c r="B163" s="35"/>
+      <c r="C163" s="35"/>
       <c r="D163" s="24">
         <v>0.15</v>
       </c>
@@ -7919,16 +7913,16 @@
       <c r="AH163" s="11"/>
       <c r="AI163" s="12"/>
       <c r="AJ163" s="13"/>
-      <c r="AK163" s="36"/>
-      <c r="AL163" s="36"/>
+      <c r="AK163" s="37"/>
+      <c r="AL163" s="37"/>
       <c r="AQ163" s="4"/>
     </row>
     <row r="164" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="42">
+      <c r="A164" s="32">
         <v>80</v>
       </c>
-      <c r="B164" s="40"/>
-      <c r="C164" s="41"/>
+      <c r="B164" s="34"/>
+      <c r="C164" s="34"/>
       <c r="D164" s="23">
         <v>0.6</v>
       </c>
@@ -7964,13 +7958,13 @@
       <c r="AH164" s="8"/>
       <c r="AI164" s="9"/>
       <c r="AJ164" s="10"/>
-      <c r="AK164" s="39"/>
-      <c r="AL164" s="39"/>
+      <c r="AK164" s="36"/>
+      <c r="AL164" s="36"/>
     </row>
     <row r="165" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="43"/>
-      <c r="B165" s="34"/>
-      <c r="C165" s="38"/>
+      <c r="A165" s="33"/>
+      <c r="B165" s="35"/>
+      <c r="C165" s="35"/>
       <c r="D165" s="24">
         <v>0.15</v>
       </c>
@@ -8006,16 +8000,16 @@
       <c r="AH165" s="11"/>
       <c r="AI165" s="12"/>
       <c r="AJ165" s="13"/>
-      <c r="AK165" s="36"/>
-      <c r="AL165" s="36"/>
+      <c r="AK165" s="37"/>
+      <c r="AL165" s="37"/>
       <c r="AQ165" s="4"/>
     </row>
     <row r="166" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="42">
+      <c r="A166" s="32">
         <v>81</v>
       </c>
-      <c r="B166" s="40"/>
-      <c r="C166" s="41"/>
+      <c r="B166" s="34"/>
+      <c r="C166" s="34"/>
       <c r="D166" s="23">
         <v>0.6</v>
       </c>
@@ -8051,13 +8045,13 @@
       <c r="AH166" s="8"/>
       <c r="AI166" s="9"/>
       <c r="AJ166" s="10"/>
-      <c r="AK166" s="39"/>
-      <c r="AL166" s="39"/>
+      <c r="AK166" s="36"/>
+      <c r="AL166" s="36"/>
     </row>
     <row r="167" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="43"/>
-      <c r="B167" s="34"/>
-      <c r="C167" s="38"/>
+      <c r="A167" s="33"/>
+      <c r="B167" s="35"/>
+      <c r="C167" s="35"/>
       <c r="D167" s="24">
         <v>0.15</v>
       </c>
@@ -8093,16 +8087,16 @@
       <c r="AH167" s="11"/>
       <c r="AI167" s="12"/>
       <c r="AJ167" s="13"/>
-      <c r="AK167" s="36"/>
-      <c r="AL167" s="36"/>
+      <c r="AK167" s="37"/>
+      <c r="AL167" s="37"/>
       <c r="AQ167" s="4"/>
     </row>
     <row r="168" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="42">
+      <c r="A168" s="32">
         <v>82</v>
       </c>
-      <c r="B168" s="40"/>
-      <c r="C168" s="41"/>
+      <c r="B168" s="34"/>
+      <c r="C168" s="34"/>
       <c r="D168" s="23">
         <v>0.6</v>
       </c>
@@ -8138,13 +8132,13 @@
       <c r="AH168" s="8"/>
       <c r="AI168" s="9"/>
       <c r="AJ168" s="10"/>
-      <c r="AK168" s="39"/>
-      <c r="AL168" s="39"/>
+      <c r="AK168" s="36"/>
+      <c r="AL168" s="36"/>
     </row>
     <row r="169" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="43"/>
-      <c r="B169" s="34"/>
-      <c r="C169" s="38"/>
+      <c r="A169" s="33"/>
+      <c r="B169" s="35"/>
+      <c r="C169" s="35"/>
       <c r="D169" s="24">
         <v>0.15</v>
       </c>
@@ -8180,16 +8174,16 @@
       <c r="AH169" s="11"/>
       <c r="AI169" s="12"/>
       <c r="AJ169" s="13"/>
-      <c r="AK169" s="36"/>
-      <c r="AL169" s="36"/>
+      <c r="AK169" s="37"/>
+      <c r="AL169" s="37"/>
       <c r="AQ169" s="4"/>
     </row>
     <row r="170" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="42">
+      <c r="A170" s="32">
         <v>83</v>
       </c>
-      <c r="B170" s="40"/>
-      <c r="C170" s="41"/>
+      <c r="B170" s="34"/>
+      <c r="C170" s="34"/>
       <c r="D170" s="23">
         <v>0.6</v>
       </c>
@@ -8225,13 +8219,13 @@
       <c r="AH170" s="8"/>
       <c r="AI170" s="9"/>
       <c r="AJ170" s="10"/>
-      <c r="AK170" s="39"/>
-      <c r="AL170" s="39"/>
+      <c r="AK170" s="36"/>
+      <c r="AL170" s="36"/>
     </row>
     <row r="171" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="43"/>
-      <c r="B171" s="34"/>
-      <c r="C171" s="38"/>
+      <c r="A171" s="33"/>
+      <c r="B171" s="35"/>
+      <c r="C171" s="35"/>
       <c r="D171" s="24">
         <v>0.15</v>
       </c>
@@ -8267,16 +8261,16 @@
       <c r="AH171" s="11"/>
       <c r="AI171" s="12"/>
       <c r="AJ171" s="13"/>
-      <c r="AK171" s="36"/>
-      <c r="AL171" s="36"/>
+      <c r="AK171" s="37"/>
+      <c r="AL171" s="37"/>
       <c r="AQ171" s="4"/>
     </row>
     <row r="172" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="42">
+      <c r="A172" s="32">
         <v>84</v>
       </c>
-      <c r="B172" s="40"/>
-      <c r="C172" s="41"/>
+      <c r="B172" s="34"/>
+      <c r="C172" s="34"/>
       <c r="D172" s="23">
         <v>0.6</v>
       </c>
@@ -8312,13 +8306,13 @@
       <c r="AH172" s="8"/>
       <c r="AI172" s="9"/>
       <c r="AJ172" s="10"/>
-      <c r="AK172" s="39"/>
-      <c r="AL172" s="39"/>
+      <c r="AK172" s="36"/>
+      <c r="AL172" s="36"/>
     </row>
     <row r="173" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="43"/>
-      <c r="B173" s="34"/>
-      <c r="C173" s="38"/>
+      <c r="A173" s="33"/>
+      <c r="B173" s="35"/>
+      <c r="C173" s="35"/>
       <c r="D173" s="24">
         <v>0.15</v>
       </c>
@@ -8354,16 +8348,16 @@
       <c r="AH173" s="11"/>
       <c r="AI173" s="12"/>
       <c r="AJ173" s="13"/>
-      <c r="AK173" s="36"/>
-      <c r="AL173" s="36"/>
+      <c r="AK173" s="37"/>
+      <c r="AL173" s="37"/>
       <c r="AQ173" s="4"/>
     </row>
     <row r="174" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="42">
+      <c r="A174" s="32">
         <v>85</v>
       </c>
-      <c r="B174" s="40"/>
-      <c r="C174" s="41"/>
+      <c r="B174" s="34"/>
+      <c r="C174" s="34"/>
       <c r="D174" s="23">
         <v>0.6</v>
       </c>
@@ -8399,13 +8393,13 @@
       <c r="AH174" s="8"/>
       <c r="AI174" s="9"/>
       <c r="AJ174" s="10"/>
-      <c r="AK174" s="39"/>
-      <c r="AL174" s="39"/>
+      <c r="AK174" s="36"/>
+      <c r="AL174" s="36"/>
     </row>
     <row r="175" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="43"/>
-      <c r="B175" s="34"/>
-      <c r="C175" s="38"/>
+      <c r="A175" s="33"/>
+      <c r="B175" s="35"/>
+      <c r="C175" s="35"/>
       <c r="D175" s="24">
         <v>0.15</v>
       </c>
@@ -8441,16 +8435,16 @@
       <c r="AH175" s="11"/>
       <c r="AI175" s="12"/>
       <c r="AJ175" s="13"/>
-      <c r="AK175" s="36"/>
-      <c r="AL175" s="36"/>
+      <c r="AK175" s="37"/>
+      <c r="AL175" s="37"/>
       <c r="AQ175" s="4"/>
     </row>
     <row r="176" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="42">
+      <c r="A176" s="32">
         <v>86</v>
       </c>
-      <c r="B176" s="40"/>
-      <c r="C176" s="41"/>
+      <c r="B176" s="34"/>
+      <c r="C176" s="34"/>
       <c r="D176" s="23">
         <v>0.6</v>
       </c>
@@ -8486,13 +8480,13 @@
       <c r="AH176" s="8"/>
       <c r="AI176" s="9"/>
       <c r="AJ176" s="10"/>
-      <c r="AK176" s="39"/>
-      <c r="AL176" s="39"/>
+      <c r="AK176" s="36"/>
+      <c r="AL176" s="36"/>
     </row>
     <row r="177" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="43"/>
-      <c r="B177" s="34"/>
-      <c r="C177" s="38"/>
+      <c r="A177" s="33"/>
+      <c r="B177" s="35"/>
+      <c r="C177" s="35"/>
       <c r="D177" s="24">
         <v>0.15</v>
       </c>
@@ -8528,16 +8522,16 @@
       <c r="AH177" s="11"/>
       <c r="AI177" s="12"/>
       <c r="AJ177" s="13"/>
-      <c r="AK177" s="36"/>
-      <c r="AL177" s="36"/>
+      <c r="AK177" s="37"/>
+      <c r="AL177" s="37"/>
       <c r="AQ177" s="4"/>
     </row>
     <row r="178" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="42">
+      <c r="A178" s="32">
         <v>87</v>
       </c>
-      <c r="B178" s="40"/>
-      <c r="C178" s="41"/>
+      <c r="B178" s="34"/>
+      <c r="C178" s="34"/>
       <c r="D178" s="23">
         <v>0.6</v>
       </c>
@@ -8573,13 +8567,13 @@
       <c r="AH178" s="8"/>
       <c r="AI178" s="9"/>
       <c r="AJ178" s="10"/>
-      <c r="AK178" s="39"/>
-      <c r="AL178" s="39"/>
+      <c r="AK178" s="36"/>
+      <c r="AL178" s="36"/>
     </row>
     <row r="179" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="43"/>
-      <c r="B179" s="34"/>
-      <c r="C179" s="38"/>
+      <c r="A179" s="33"/>
+      <c r="B179" s="35"/>
+      <c r="C179" s="35"/>
       <c r="D179" s="24">
         <v>0.15</v>
       </c>
@@ -8615,16 +8609,16 @@
       <c r="AH179" s="11"/>
       <c r="AI179" s="12"/>
       <c r="AJ179" s="13"/>
-      <c r="AK179" s="36"/>
-      <c r="AL179" s="36"/>
+      <c r="AK179" s="37"/>
+      <c r="AL179" s="37"/>
       <c r="AQ179" s="4"/>
     </row>
     <row r="180" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="42">
+      <c r="A180" s="32">
         <v>88</v>
       </c>
-      <c r="B180" s="40"/>
-      <c r="C180" s="41"/>
+      <c r="B180" s="34"/>
+      <c r="C180" s="34"/>
       <c r="D180" s="23">
         <v>0.6</v>
       </c>
@@ -8660,13 +8654,13 @@
       <c r="AH180" s="8"/>
       <c r="AI180" s="9"/>
       <c r="AJ180" s="10"/>
-      <c r="AK180" s="39"/>
-      <c r="AL180" s="39"/>
+      <c r="AK180" s="36"/>
+      <c r="AL180" s="36"/>
     </row>
     <row r="181" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="43"/>
-      <c r="B181" s="34"/>
-      <c r="C181" s="38"/>
+      <c r="A181" s="33"/>
+      <c r="B181" s="35"/>
+      <c r="C181" s="35"/>
       <c r="D181" s="24">
         <v>0.15</v>
       </c>
@@ -8702,16 +8696,16 @@
       <c r="AH181" s="11"/>
       <c r="AI181" s="12"/>
       <c r="AJ181" s="13"/>
-      <c r="AK181" s="36"/>
-      <c r="AL181" s="36"/>
+      <c r="AK181" s="37"/>
+      <c r="AL181" s="37"/>
       <c r="AQ181" s="4"/>
     </row>
     <row r="182" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="42">
+      <c r="A182" s="32">
         <v>89</v>
       </c>
-      <c r="B182" s="40"/>
-      <c r="C182" s="41"/>
+      <c r="B182" s="34"/>
+      <c r="C182" s="34"/>
       <c r="D182" s="23">
         <v>0.6</v>
       </c>
@@ -8747,13 +8741,13 @@
       <c r="AH182" s="8"/>
       <c r="AI182" s="9"/>
       <c r="AJ182" s="10"/>
-      <c r="AK182" s="39"/>
-      <c r="AL182" s="39"/>
+      <c r="AK182" s="36"/>
+      <c r="AL182" s="36"/>
     </row>
     <row r="183" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="43"/>
-      <c r="B183" s="34"/>
-      <c r="C183" s="38"/>
+      <c r="A183" s="33"/>
+      <c r="B183" s="35"/>
+      <c r="C183" s="35"/>
       <c r="D183" s="24">
         <v>0.15</v>
       </c>
@@ -8789,16 +8783,16 @@
       <c r="AH183" s="11"/>
       <c r="AI183" s="12"/>
       <c r="AJ183" s="13"/>
-      <c r="AK183" s="36"/>
-      <c r="AL183" s="36"/>
+      <c r="AK183" s="37"/>
+      <c r="AL183" s="37"/>
       <c r="AQ183" s="4"/>
     </row>
     <row r="184" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="42">
+      <c r="A184" s="32">
         <v>90</v>
       </c>
-      <c r="B184" s="40"/>
-      <c r="C184" s="41"/>
+      <c r="B184" s="34"/>
+      <c r="C184" s="34"/>
       <c r="D184" s="23">
         <v>0.6</v>
       </c>
@@ -8834,13 +8828,13 @@
       <c r="AH184" s="8"/>
       <c r="AI184" s="9"/>
       <c r="AJ184" s="10"/>
-      <c r="AK184" s="39"/>
-      <c r="AL184" s="39"/>
+      <c r="AK184" s="36"/>
+      <c r="AL184" s="36"/>
     </row>
     <row r="185" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="43"/>
-      <c r="B185" s="34"/>
-      <c r="C185" s="38"/>
+      <c r="A185" s="33"/>
+      <c r="B185" s="35"/>
+      <c r="C185" s="35"/>
       <c r="D185" s="24">
         <v>0.15</v>
       </c>
@@ -8876,16 +8870,16 @@
       <c r="AH185" s="11"/>
       <c r="AI185" s="12"/>
       <c r="AJ185" s="13"/>
-      <c r="AK185" s="36"/>
-      <c r="AL185" s="36"/>
+      <c r="AK185" s="37"/>
+      <c r="AL185" s="37"/>
       <c r="AQ185" s="4"/>
     </row>
     <row r="186" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="42">
+      <c r="A186" s="32">
         <v>91</v>
       </c>
-      <c r="B186" s="40"/>
-      <c r="C186" s="41"/>
+      <c r="B186" s="34"/>
+      <c r="C186" s="34"/>
       <c r="D186" s="23">
         <v>0.6</v>
       </c>
@@ -8921,13 +8915,13 @@
       <c r="AH186" s="8"/>
       <c r="AI186" s="9"/>
       <c r="AJ186" s="10"/>
-      <c r="AK186" s="39"/>
-      <c r="AL186" s="39"/>
+      <c r="AK186" s="36"/>
+      <c r="AL186" s="36"/>
     </row>
     <row r="187" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="43"/>
-      <c r="B187" s="34"/>
-      <c r="C187" s="38"/>
+      <c r="A187" s="33"/>
+      <c r="B187" s="35"/>
+      <c r="C187" s="35"/>
       <c r="D187" s="24">
         <v>0.15</v>
       </c>
@@ -8963,16 +8957,16 @@
       <c r="AH187" s="11"/>
       <c r="AI187" s="12"/>
       <c r="AJ187" s="13"/>
-      <c r="AK187" s="36"/>
-      <c r="AL187" s="36"/>
+      <c r="AK187" s="37"/>
+      <c r="AL187" s="37"/>
       <c r="AQ187" s="4"/>
     </row>
     <row r="188" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="42">
+      <c r="A188" s="32">
         <v>92</v>
       </c>
-      <c r="B188" s="40"/>
-      <c r="C188" s="41"/>
+      <c r="B188" s="34"/>
+      <c r="C188" s="34"/>
       <c r="D188" s="23">
         <v>0.6</v>
       </c>
@@ -9008,13 +9002,13 @@
       <c r="AH188" s="8"/>
       <c r="AI188" s="9"/>
       <c r="AJ188" s="10"/>
-      <c r="AK188" s="39"/>
-      <c r="AL188" s="39"/>
+      <c r="AK188" s="36"/>
+      <c r="AL188" s="36"/>
     </row>
     <row r="189" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="43"/>
-      <c r="B189" s="34"/>
-      <c r="C189" s="38"/>
+      <c r="A189" s="33"/>
+      <c r="B189" s="35"/>
+      <c r="C189" s="35"/>
       <c r="D189" s="24">
         <v>0.15</v>
       </c>
@@ -9050,16 +9044,16 @@
       <c r="AH189" s="11"/>
       <c r="AI189" s="12"/>
       <c r="AJ189" s="13"/>
-      <c r="AK189" s="36"/>
-      <c r="AL189" s="36"/>
+      <c r="AK189" s="37"/>
+      <c r="AL189" s="37"/>
       <c r="AQ189" s="4"/>
     </row>
     <row r="190" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="42">
+      <c r="A190" s="32">
         <v>93</v>
       </c>
-      <c r="B190" s="40"/>
-      <c r="C190" s="41"/>
+      <c r="B190" s="34"/>
+      <c r="C190" s="34"/>
       <c r="D190" s="23">
         <v>0.6</v>
       </c>
@@ -9095,13 +9089,13 @@
       <c r="AH190" s="8"/>
       <c r="AI190" s="9"/>
       <c r="AJ190" s="10"/>
-      <c r="AK190" s="39"/>
-      <c r="AL190" s="39"/>
+      <c r="AK190" s="36"/>
+      <c r="AL190" s="36"/>
     </row>
     <row r="191" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="43"/>
-      <c r="B191" s="34"/>
-      <c r="C191" s="38"/>
+      <c r="A191" s="33"/>
+      <c r="B191" s="35"/>
+      <c r="C191" s="35"/>
       <c r="D191" s="24">
         <v>0.15</v>
       </c>
@@ -9137,16 +9131,16 @@
       <c r="AH191" s="11"/>
       <c r="AI191" s="12"/>
       <c r="AJ191" s="13"/>
-      <c r="AK191" s="36"/>
-      <c r="AL191" s="36"/>
+      <c r="AK191" s="37"/>
+      <c r="AL191" s="37"/>
       <c r="AQ191" s="4"/>
     </row>
     <row r="192" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="42">
+      <c r="A192" s="32">
         <v>94</v>
       </c>
-      <c r="B192" s="40"/>
-      <c r="C192" s="41"/>
+      <c r="B192" s="34"/>
+      <c r="C192" s="34"/>
       <c r="D192" s="23">
         <v>0.6</v>
       </c>
@@ -9182,13 +9176,13 @@
       <c r="AH192" s="8"/>
       <c r="AI192" s="9"/>
       <c r="AJ192" s="10"/>
-      <c r="AK192" s="39"/>
-      <c r="AL192" s="39"/>
+      <c r="AK192" s="36"/>
+      <c r="AL192" s="36"/>
     </row>
     <row r="193" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="43"/>
-      <c r="B193" s="34"/>
-      <c r="C193" s="38"/>
+      <c r="A193" s="33"/>
+      <c r="B193" s="35"/>
+      <c r="C193" s="35"/>
       <c r="D193" s="24">
         <v>0.15</v>
       </c>
@@ -9224,16 +9218,16 @@
       <c r="AH193" s="11"/>
       <c r="AI193" s="12"/>
       <c r="AJ193" s="13"/>
-      <c r="AK193" s="36"/>
-      <c r="AL193" s="36"/>
+      <c r="AK193" s="37"/>
+      <c r="AL193" s="37"/>
       <c r="AQ193" s="4"/>
     </row>
     <row r="194" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="42">
+      <c r="A194" s="32">
         <v>95</v>
       </c>
-      <c r="B194" s="40"/>
-      <c r="C194" s="41"/>
+      <c r="B194" s="34"/>
+      <c r="C194" s="34"/>
       <c r="D194" s="23">
         <v>0.6</v>
       </c>
@@ -9269,13 +9263,13 @@
       <c r="AH194" s="8"/>
       <c r="AI194" s="9"/>
       <c r="AJ194" s="10"/>
-      <c r="AK194" s="39"/>
-      <c r="AL194" s="39"/>
+      <c r="AK194" s="36"/>
+      <c r="AL194" s="36"/>
     </row>
     <row r="195" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="43"/>
-      <c r="B195" s="34"/>
-      <c r="C195" s="38"/>
+      <c r="A195" s="33"/>
+      <c r="B195" s="35"/>
+      <c r="C195" s="35"/>
       <c r="D195" s="24">
         <v>0.15</v>
       </c>
@@ -9311,16 +9305,16 @@
       <c r="AH195" s="11"/>
       <c r="AI195" s="12"/>
       <c r="AJ195" s="13"/>
-      <c r="AK195" s="36"/>
-      <c r="AL195" s="36"/>
+      <c r="AK195" s="37"/>
+      <c r="AL195" s="37"/>
       <c r="AQ195" s="4"/>
     </row>
     <row r="196" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="42">
+      <c r="A196" s="32">
         <v>96</v>
       </c>
-      <c r="B196" s="40"/>
-      <c r="C196" s="41"/>
+      <c r="B196" s="34"/>
+      <c r="C196" s="34"/>
       <c r="D196" s="23">
         <v>0.6</v>
       </c>
@@ -9356,13 +9350,13 @@
       <c r="AH196" s="8"/>
       <c r="AI196" s="9"/>
       <c r="AJ196" s="10"/>
-      <c r="AK196" s="39"/>
-      <c r="AL196" s="39"/>
+      <c r="AK196" s="36"/>
+      <c r="AL196" s="36"/>
     </row>
     <row r="197" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="43"/>
-      <c r="B197" s="34"/>
-      <c r="C197" s="38"/>
+      <c r="A197" s="33"/>
+      <c r="B197" s="35"/>
+      <c r="C197" s="35"/>
       <c r="D197" s="24">
         <v>0.15</v>
       </c>
@@ -9398,16 +9392,16 @@
       <c r="AH197" s="11"/>
       <c r="AI197" s="12"/>
       <c r="AJ197" s="13"/>
-      <c r="AK197" s="36"/>
-      <c r="AL197" s="36"/>
+      <c r="AK197" s="37"/>
+      <c r="AL197" s="37"/>
       <c r="AQ197" s="4"/>
     </row>
     <row r="198" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="42">
+      <c r="A198" s="32">
         <v>97</v>
       </c>
-      <c r="B198" s="40"/>
-      <c r="C198" s="41"/>
+      <c r="B198" s="34"/>
+      <c r="C198" s="34"/>
       <c r="D198" s="23">
         <v>0.6</v>
       </c>
@@ -9443,13 +9437,13 @@
       <c r="AH198" s="8"/>
       <c r="AI198" s="9"/>
       <c r="AJ198" s="10"/>
-      <c r="AK198" s="39"/>
-      <c r="AL198" s="39"/>
+      <c r="AK198" s="36"/>
+      <c r="AL198" s="36"/>
     </row>
     <row r="199" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="43"/>
-      <c r="B199" s="34"/>
-      <c r="C199" s="38"/>
+      <c r="A199" s="33"/>
+      <c r="B199" s="35"/>
+      <c r="C199" s="35"/>
       <c r="D199" s="24">
         <v>0.15</v>
       </c>
@@ -9485,16 +9479,16 @@
       <c r="AH199" s="11"/>
       <c r="AI199" s="12"/>
       <c r="AJ199" s="13"/>
-      <c r="AK199" s="36"/>
-      <c r="AL199" s="36"/>
+      <c r="AK199" s="37"/>
+      <c r="AL199" s="37"/>
       <c r="AQ199" s="4"/>
     </row>
     <row r="200" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="42">
+      <c r="A200" s="32">
         <v>98</v>
       </c>
-      <c r="B200" s="40"/>
-      <c r="C200" s="41"/>
+      <c r="B200" s="34"/>
+      <c r="C200" s="34"/>
       <c r="D200" s="23">
         <v>0.6</v>
       </c>
@@ -9530,13 +9524,13 @@
       <c r="AH200" s="8"/>
       <c r="AI200" s="9"/>
       <c r="AJ200" s="10"/>
-      <c r="AK200" s="39"/>
-      <c r="AL200" s="39"/>
+      <c r="AK200" s="36"/>
+      <c r="AL200" s="36"/>
     </row>
     <row r="201" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="43"/>
-      <c r="B201" s="34"/>
-      <c r="C201" s="38"/>
+      <c r="A201" s="33"/>
+      <c r="B201" s="35"/>
+      <c r="C201" s="35"/>
       <c r="D201" s="24">
         <v>0.15</v>
       </c>
@@ -9572,16 +9566,16 @@
       <c r="AH201" s="11"/>
       <c r="AI201" s="12"/>
       <c r="AJ201" s="13"/>
-      <c r="AK201" s="36"/>
-      <c r="AL201" s="36"/>
+      <c r="AK201" s="37"/>
+      <c r="AL201" s="37"/>
       <c r="AQ201" s="4"/>
     </row>
     <row r="202" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="42">
+      <c r="A202" s="32">
         <v>99</v>
       </c>
-      <c r="B202" s="40"/>
-      <c r="C202" s="41"/>
+      <c r="B202" s="34"/>
+      <c r="C202" s="34"/>
       <c r="D202" s="23">
         <v>0.6</v>
       </c>
@@ -9617,13 +9611,13 @@
       <c r="AH202" s="8"/>
       <c r="AI202" s="9"/>
       <c r="AJ202" s="10"/>
-      <c r="AK202" s="39"/>
-      <c r="AL202" s="39"/>
+      <c r="AK202" s="36"/>
+      <c r="AL202" s="36"/>
     </row>
     <row r="203" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="43"/>
-      <c r="B203" s="34"/>
-      <c r="C203" s="38"/>
+      <c r="A203" s="33"/>
+      <c r="B203" s="35"/>
+      <c r="C203" s="35"/>
       <c r="D203" s="24">
         <v>0.15</v>
       </c>
@@ -9659,16 +9653,16 @@
       <c r="AH203" s="11"/>
       <c r="AI203" s="12"/>
       <c r="AJ203" s="13"/>
-      <c r="AK203" s="36"/>
-      <c r="AL203" s="36"/>
+      <c r="AK203" s="37"/>
+      <c r="AL203" s="37"/>
       <c r="AQ203" s="4"/>
     </row>
     <row r="204" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="42">
+      <c r="A204" s="32">
         <v>100</v>
       </c>
-      <c r="B204" s="40"/>
-      <c r="C204" s="41"/>
+      <c r="B204" s="34"/>
+      <c r="C204" s="34"/>
       <c r="D204" s="23">
         <v>0.6</v>
       </c>
@@ -9704,13 +9698,13 @@
       <c r="AH204" s="8"/>
       <c r="AI204" s="9"/>
       <c r="AJ204" s="10"/>
-      <c r="AK204" s="39"/>
-      <c r="AL204" s="39"/>
+      <c r="AK204" s="36"/>
+      <c r="AL204" s="36"/>
     </row>
     <row r="205" spans="1:43" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="43"/>
-      <c r="B205" s="34"/>
-      <c r="C205" s="38"/>
+      <c r="A205" s="33"/>
+      <c r="B205" s="35"/>
+      <c r="C205" s="35"/>
       <c r="D205" s="24">
         <v>0.15</v>
       </c>
@@ -9746,50 +9740,50 @@
       <c r="AH205" s="11"/>
       <c r="AI205" s="12"/>
       <c r="AJ205" s="13"/>
-      <c r="AK205" s="36"/>
-      <c r="AL205" s="36"/>
+      <c r="AK205" s="37"/>
+      <c r="AL205" s="37"/>
       <c r="AQ205" s="4"/>
     </row>
     <row r="206" spans="1:43" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B206" s="44" t="s">
+      <c r="B206" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C206" s="44"/>
-      <c r="D206" s="44"/>
-      <c r="E206" s="44"/>
-      <c r="F206" s="44"/>
-      <c r="G206" s="44"/>
-      <c r="H206" s="44"/>
-      <c r="I206" s="44"/>
-      <c r="J206" s="44"/>
-      <c r="K206" s="44"/>
-      <c r="L206" s="44"/>
-      <c r="M206" s="44"/>
-      <c r="N206" s="44"/>
-      <c r="O206" s="44"/>
-      <c r="P206" s="44"/>
-      <c r="Q206" s="44"/>
-      <c r="R206" s="44"/>
-      <c r="S206" s="44"/>
-      <c r="T206" s="44"/>
-      <c r="U206" s="44"/>
-      <c r="V206" s="44"/>
-      <c r="W206" s="44"/>
-      <c r="X206" s="44"/>
-      <c r="Y206" s="44"/>
-      <c r="Z206" s="44"/>
-      <c r="AA206" s="44"/>
-      <c r="AB206" s="44"/>
-      <c r="AC206" s="44"/>
-      <c r="AD206" s="44"/>
-      <c r="AE206" s="44"/>
-      <c r="AF206" s="44"/>
-      <c r="AG206" s="44"/>
-      <c r="AH206" s="44"/>
-      <c r="AI206" s="44"/>
-      <c r="AJ206" s="44"/>
-      <c r="AK206" s="44"/>
-      <c r="AL206" s="44"/>
+      <c r="C206" s="41"/>
+      <c r="D206" s="41"/>
+      <c r="E206" s="41"/>
+      <c r="F206" s="41"/>
+      <c r="G206" s="41"/>
+      <c r="H206" s="41"/>
+      <c r="I206" s="41"/>
+      <c r="J206" s="41"/>
+      <c r="K206" s="41"/>
+      <c r="L206" s="41"/>
+      <c r="M206" s="41"/>
+      <c r="N206" s="41"/>
+      <c r="O206" s="41"/>
+      <c r="P206" s="41"/>
+      <c r="Q206" s="41"/>
+      <c r="R206" s="41"/>
+      <c r="S206" s="41"/>
+      <c r="T206" s="41"/>
+      <c r="U206" s="41"/>
+      <c r="V206" s="41"/>
+      <c r="W206" s="41"/>
+      <c r="X206" s="41"/>
+      <c r="Y206" s="41"/>
+      <c r="Z206" s="41"/>
+      <c r="AA206" s="41"/>
+      <c r="AB206" s="41"/>
+      <c r="AC206" s="41"/>
+      <c r="AD206" s="41"/>
+      <c r="AE206" s="41"/>
+      <c r="AF206" s="41"/>
+      <c r="AG206" s="41"/>
+      <c r="AH206" s="41"/>
+      <c r="AI206" s="41"/>
+      <c r="AJ206" s="41"/>
+      <c r="AK206" s="41"/>
+      <c r="AL206" s="41"/>
     </row>
     <row r="207" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C207" s="2"/>
@@ -9832,27 +9826,27 @@
     <row r="210" spans="1:39" s="3" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A210" s="21"/>
       <c r="B210" s="22"/>
-      <c r="C210" s="32" t="s">
+      <c r="C210" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D210" s="32"/>
-      <c r="E210" s="32"/>
+      <c r="D210" s="40"/>
+      <c r="E210" s="40"/>
       <c r="F210" s="7"/>
       <c r="G210" s="7"/>
       <c r="H210" s="7"/>
       <c r="I210" s="14"/>
       <c r="J210" s="15"/>
-      <c r="K210" s="32" t="s">
+      <c r="K210" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="L210" s="32"/>
-      <c r="M210" s="32"/>
-      <c r="N210" s="32"/>
-      <c r="O210" s="32"/>
-      <c r="P210" s="32"/>
-      <c r="Q210" s="32"/>
-      <c r="R210" s="32"/>
-      <c r="S210" s="32"/>
+      <c r="L210" s="40"/>
+      <c r="M210" s="40"/>
+      <c r="N210" s="40"/>
+      <c r="O210" s="40"/>
+      <c r="P210" s="40"/>
+      <c r="Q210" s="40"/>
+      <c r="R210" s="40"/>
+      <c r="S210" s="40"/>
       <c r="T210" s="15"/>
       <c r="U210" s="15"/>
       <c r="V210" s="15"/>
@@ -9860,18 +9854,18 @@
       <c r="X210" s="15"/>
       <c r="Y210" s="15"/>
       <c r="Z210" s="15"/>
-      <c r="AA210" s="32" t="s">
+      <c r="AA210" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="AB210" s="32"/>
-      <c r="AC210" s="32"/>
-      <c r="AD210" s="32"/>
-      <c r="AE210" s="32"/>
-      <c r="AF210" s="32"/>
-      <c r="AG210" s="32"/>
-      <c r="AH210" s="32"/>
-      <c r="AI210" s="32"/>
-      <c r="AJ210" s="32"/>
+      <c r="AB210" s="40"/>
+      <c r="AC210" s="40"/>
+      <c r="AD210" s="40"/>
+      <c r="AE210" s="40"/>
+      <c r="AF210" s="40"/>
+      <c r="AG210" s="40"/>
+      <c r="AH210" s="40"/>
+      <c r="AI210" s="40"/>
+      <c r="AJ210" s="40"/>
       <c r="AK210" s="16"/>
       <c r="AL210" s="17"/>
       <c r="AM210" s="17"/>
@@ -9879,25 +9873,25 @@
     <row r="211" spans="1:39" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="22"/>
       <c r="B211" s="22"/>
-      <c r="C211" s="32" t="s">
+      <c r="C211" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="D211" s="32"/>
-      <c r="E211" s="32"/>
+      <c r="D211" s="40"/>
+      <c r="E211" s="40"/>
       <c r="F211" s="5"/>
       <c r="G211" s="5"/>
       <c r="H211" s="5"/>
       <c r="I211" s="31"/>
       <c r="J211" s="31"/>
-      <c r="K211" s="32"/>
-      <c r="L211" s="32"/>
-      <c r="M211" s="32"/>
-      <c r="N211" s="32"/>
-      <c r="O211" s="32"/>
-      <c r="P211" s="32"/>
-      <c r="Q211" s="32"/>
-      <c r="R211" s="32"/>
-      <c r="S211" s="32"/>
+      <c r="K211" s="40"/>
+      <c r="L211" s="40"/>
+      <c r="M211" s="40"/>
+      <c r="N211" s="40"/>
+      <c r="O211" s="40"/>
+      <c r="P211" s="40"/>
+      <c r="Q211" s="40"/>
+      <c r="R211" s="40"/>
+      <c r="S211" s="40"/>
       <c r="T211" s="31"/>
       <c r="U211" s="14"/>
       <c r="V211" s="14"/>
@@ -9905,16 +9899,16 @@
       <c r="X211" s="14"/>
       <c r="Y211" s="14"/>
       <c r="Z211" s="14"/>
-      <c r="AA211" s="32"/>
-      <c r="AB211" s="32"/>
-      <c r="AC211" s="32"/>
-      <c r="AD211" s="32"/>
-      <c r="AE211" s="32"/>
-      <c r="AF211" s="32"/>
-      <c r="AG211" s="32"/>
-      <c r="AH211" s="32"/>
-      <c r="AI211" s="32"/>
-      <c r="AJ211" s="32"/>
+      <c r="AA211" s="40"/>
+      <c r="AB211" s="40"/>
+      <c r="AC211" s="40"/>
+      <c r="AD211" s="40"/>
+      <c r="AE211" s="40"/>
+      <c r="AF211" s="40"/>
+      <c r="AG211" s="40"/>
+      <c r="AH211" s="40"/>
+      <c r="AI211" s="40"/>
+      <c r="AJ211" s="40"/>
       <c r="AK211" s="14"/>
       <c r="AL211" s="14"/>
       <c r="AM211" s="14"/>
@@ -9954,467 +9948,30 @@
     </row>
   </sheetData>
   <mergeCells count="509">
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="AK202:AK203"/>
-    <mergeCell ref="AL202:AL203"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="AK204:AK205"/>
-    <mergeCell ref="AL204:AL205"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="AK198:AK199"/>
-    <mergeCell ref="AL198:AL199"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="AK200:AK201"/>
-    <mergeCell ref="AL200:AL201"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="C194:C195"/>
-    <mergeCell ref="AK194:AK195"/>
-    <mergeCell ref="AL194:AL195"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="AK196:AK197"/>
-    <mergeCell ref="AL196:AL197"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="AK190:AK191"/>
-    <mergeCell ref="AL190:AL191"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="C192:C193"/>
-    <mergeCell ref="AK192:AK193"/>
-    <mergeCell ref="AL192:AL193"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="AK186:AK187"/>
-    <mergeCell ref="AL186:AL187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="AK188:AK189"/>
-    <mergeCell ref="AL188:AL189"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="C182:C183"/>
-    <mergeCell ref="AK182:AK183"/>
-    <mergeCell ref="AL182:AL183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="AK184:AK185"/>
-    <mergeCell ref="AL184:AL185"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="AK178:AK179"/>
-    <mergeCell ref="AL178:AL179"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="C180:C181"/>
-    <mergeCell ref="AK180:AK181"/>
-    <mergeCell ref="AL180:AL181"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="AK174:AK175"/>
-    <mergeCell ref="AL174:AL175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="C176:C177"/>
-    <mergeCell ref="AK176:AK177"/>
-    <mergeCell ref="AL176:AL177"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="AK170:AK171"/>
-    <mergeCell ref="AL170:AL171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="AK172:AK173"/>
-    <mergeCell ref="AL172:AL173"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="AK166:AK167"/>
-    <mergeCell ref="AL166:AL167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="AK168:AK169"/>
-    <mergeCell ref="AL168:AL169"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="AK162:AK163"/>
-    <mergeCell ref="AL162:AL163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="AK164:AK165"/>
-    <mergeCell ref="AL164:AL165"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="AK157:AK158"/>
-    <mergeCell ref="AL157:AL158"/>
-    <mergeCell ref="A159:A160"/>
-    <mergeCell ref="B159:B160"/>
-    <mergeCell ref="C159:C160"/>
-    <mergeCell ref="AK159:AK160"/>
-    <mergeCell ref="AL159:AL160"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="C153:C154"/>
-    <mergeCell ref="AK153:AK154"/>
-    <mergeCell ref="AL153:AL154"/>
-    <mergeCell ref="A155:A156"/>
-    <mergeCell ref="B155:B156"/>
-    <mergeCell ref="C155:C156"/>
-    <mergeCell ref="AK155:AK156"/>
-    <mergeCell ref="AL155:AL156"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="B149:B150"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="AK149:AK150"/>
-    <mergeCell ref="AL149:AL150"/>
-    <mergeCell ref="A151:A152"/>
-    <mergeCell ref="B151:B152"/>
-    <mergeCell ref="C151:C152"/>
-    <mergeCell ref="AK151:AK152"/>
-    <mergeCell ref="AL151:AL152"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="AK145:AK146"/>
-    <mergeCell ref="AL145:AL146"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="C147:C148"/>
-    <mergeCell ref="AK147:AK148"/>
-    <mergeCell ref="AL147:AL148"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="AK141:AK142"/>
-    <mergeCell ref="AL141:AL142"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="AK143:AK144"/>
-    <mergeCell ref="AL143:AL144"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="AK137:AK138"/>
-    <mergeCell ref="AL137:AL138"/>
-    <mergeCell ref="A139:A140"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="C139:C140"/>
-    <mergeCell ref="AK139:AK140"/>
-    <mergeCell ref="AL139:AL140"/>
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="AK133:AK134"/>
-    <mergeCell ref="AL133:AL134"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="B135:B136"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="AK135:AK136"/>
-    <mergeCell ref="AL135:AL136"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B129:B130"/>
-    <mergeCell ref="C129:C130"/>
-    <mergeCell ref="AK129:AK130"/>
-    <mergeCell ref="AL129:AL130"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="C131:C132"/>
-    <mergeCell ref="AK131:AK132"/>
-    <mergeCell ref="AL131:AL132"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="C125:C126"/>
-    <mergeCell ref="AK125:AK126"/>
-    <mergeCell ref="AL125:AL126"/>
-    <mergeCell ref="A127:A128"/>
-    <mergeCell ref="B127:B128"/>
-    <mergeCell ref="C127:C128"/>
-    <mergeCell ref="AK127:AK128"/>
-    <mergeCell ref="AL127:AL128"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="AK121:AK122"/>
-    <mergeCell ref="AL121:AL122"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="AK123:AK124"/>
-    <mergeCell ref="AL123:AL124"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="AK117:AK118"/>
-    <mergeCell ref="AL117:AL118"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="AK119:AK120"/>
-    <mergeCell ref="AL119:AL120"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="AK113:AK114"/>
-    <mergeCell ref="AL113:AL114"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="AK115:AK116"/>
-    <mergeCell ref="AL115:AL116"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="AK109:AK110"/>
-    <mergeCell ref="AL109:AL110"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="AK111:AK112"/>
-    <mergeCell ref="AL111:AL112"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="AK105:AK106"/>
-    <mergeCell ref="AL105:AL106"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="AK107:AK108"/>
-    <mergeCell ref="AL107:AL108"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="AK101:AK102"/>
-    <mergeCell ref="AL101:AL102"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="C103:C104"/>
-    <mergeCell ref="AK103:AK104"/>
-    <mergeCell ref="AL103:AL104"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="AK97:AK98"/>
-    <mergeCell ref="AL97:AL98"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="AK99:AK100"/>
-    <mergeCell ref="AL99:AL100"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="AK93:AK94"/>
-    <mergeCell ref="AL93:AL94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="AK95:AK96"/>
-    <mergeCell ref="AL95:AL96"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="AK89:AK90"/>
-    <mergeCell ref="AL89:AL90"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="AK91:AK92"/>
-    <mergeCell ref="AL91:AL92"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="AK85:AK86"/>
-    <mergeCell ref="AL85:AL86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="AK87:AK88"/>
-    <mergeCell ref="AL87:AL88"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="AK81:AK82"/>
-    <mergeCell ref="AL81:AL82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="AK83:AK84"/>
-    <mergeCell ref="AL83:AL84"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="AK77:AK78"/>
-    <mergeCell ref="AL77:AL78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="AK79:AK80"/>
-    <mergeCell ref="AL79:AL80"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="AK73:AK74"/>
-    <mergeCell ref="AL73:AL74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="AK75:AK76"/>
-    <mergeCell ref="AL75:AL76"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="AK69:AK70"/>
-    <mergeCell ref="AL69:AL70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="AK71:AK72"/>
-    <mergeCell ref="AL71:AL72"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="AK65:AK66"/>
-    <mergeCell ref="AL65:AL66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="AK67:AK68"/>
-    <mergeCell ref="AL67:AL68"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="AK61:AK62"/>
-    <mergeCell ref="AL61:AL62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="AK63:AK64"/>
-    <mergeCell ref="AL63:AL64"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="AK57:AK58"/>
-    <mergeCell ref="AL57:AL58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="AK59:AK60"/>
-    <mergeCell ref="AL59:AL60"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="AK4:AK5"/>
-    <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="AK6:AK7"/>
-    <mergeCell ref="AL6:AL7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="AK10:AK11"/>
-    <mergeCell ref="AL10:AL11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="AK12:AK13"/>
-    <mergeCell ref="AL12:AL13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="AK14:AK15"/>
-    <mergeCell ref="AL14:AL15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="AK16:AK17"/>
-    <mergeCell ref="AL16:AL17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="AK18:AK19"/>
-    <mergeCell ref="AL18:AL19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="AK20:AK21"/>
-    <mergeCell ref="AL20:AL21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="AK22:AK23"/>
-    <mergeCell ref="AL22:AL23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="AK24:AK25"/>
-    <mergeCell ref="AL24:AL25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="AK26:AK27"/>
-    <mergeCell ref="AL26:AL27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="AK28:AK29"/>
-    <mergeCell ref="AL28:AL29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="AK30:AK31"/>
-    <mergeCell ref="AL30:AL31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="AK32:AK33"/>
-    <mergeCell ref="AL32:AL33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="AK34:AK35"/>
-    <mergeCell ref="AL34:AL35"/>
-    <mergeCell ref="AL42:AL43"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="AK36:AK37"/>
-    <mergeCell ref="AL36:AL37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="AK38:AK39"/>
-    <mergeCell ref="AL38:AL39"/>
+    <mergeCell ref="C211:E211"/>
+    <mergeCell ref="K210:S210"/>
+    <mergeCell ref="AA210:AJ210"/>
+    <mergeCell ref="AA211:AJ211"/>
+    <mergeCell ref="K211:S211"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="AK54:AK55"/>
+    <mergeCell ref="AL54:AL55"/>
+    <mergeCell ref="D2:AE2"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="AL44:AL45"/>
+    <mergeCell ref="AL52:AL53"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="AK44:AK45"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="AK52:AK53"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="AK50:AK51"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="AK46:AK47"/>
     <mergeCell ref="AL50:AL51"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="B48:B49"/>
@@ -10439,30 +9996,467 @@
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="AK42:AK43"/>
-    <mergeCell ref="C211:E211"/>
-    <mergeCell ref="K210:S210"/>
-    <mergeCell ref="AA210:AJ210"/>
-    <mergeCell ref="AA211:AJ211"/>
-    <mergeCell ref="K211:S211"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="AK54:AK55"/>
-    <mergeCell ref="AL54:AL55"/>
-    <mergeCell ref="D2:AE2"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="AL44:AL45"/>
-    <mergeCell ref="AL52:AL53"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="AK44:AK45"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="AK52:AK53"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="AK50:AK51"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="AK46:AK47"/>
+    <mergeCell ref="AL42:AL43"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="AK36:AK37"/>
+    <mergeCell ref="AL36:AL37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="AK38:AK39"/>
+    <mergeCell ref="AL38:AL39"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="AK32:AK33"/>
+    <mergeCell ref="AL32:AL33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="AK34:AK35"/>
+    <mergeCell ref="AL34:AL35"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="AK28:AK29"/>
+    <mergeCell ref="AL28:AL29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="AK30:AK31"/>
+    <mergeCell ref="AL30:AL31"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="AK24:AK25"/>
+    <mergeCell ref="AL24:AL25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="AK26:AK27"/>
+    <mergeCell ref="AL26:AL27"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="AK20:AK21"/>
+    <mergeCell ref="AL20:AL21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="AK22:AK23"/>
+    <mergeCell ref="AL22:AL23"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="AK16:AK17"/>
+    <mergeCell ref="AL16:AL17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="AK18:AK19"/>
+    <mergeCell ref="AL18:AL19"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="AK12:AK13"/>
+    <mergeCell ref="AL12:AL13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="AK14:AK15"/>
+    <mergeCell ref="AL14:AL15"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="AK10:AK11"/>
+    <mergeCell ref="AL10:AL11"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="AK4:AK5"/>
+    <mergeCell ref="AL4:AL5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="AK6:AK7"/>
+    <mergeCell ref="AL6:AL7"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="AK57:AK58"/>
+    <mergeCell ref="AL57:AL58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="AK59:AK60"/>
+    <mergeCell ref="AL59:AL60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="AK61:AK62"/>
+    <mergeCell ref="AL61:AL62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="AK63:AK64"/>
+    <mergeCell ref="AL63:AL64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="AK65:AK66"/>
+    <mergeCell ref="AL65:AL66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="AK67:AK68"/>
+    <mergeCell ref="AL67:AL68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="AK69:AK70"/>
+    <mergeCell ref="AL69:AL70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="AK71:AK72"/>
+    <mergeCell ref="AL71:AL72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="AK73:AK74"/>
+    <mergeCell ref="AL73:AL74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="AK75:AK76"/>
+    <mergeCell ref="AL75:AL76"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="AK77:AK78"/>
+    <mergeCell ref="AL77:AL78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="AK79:AK80"/>
+    <mergeCell ref="AL79:AL80"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="AK81:AK82"/>
+    <mergeCell ref="AL81:AL82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="AK83:AK84"/>
+    <mergeCell ref="AL83:AL84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="AK85:AK86"/>
+    <mergeCell ref="AL85:AL86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="AK87:AK88"/>
+    <mergeCell ref="AL87:AL88"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="AK89:AK90"/>
+    <mergeCell ref="AL89:AL90"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="AK91:AK92"/>
+    <mergeCell ref="AL91:AL92"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="AK93:AK94"/>
+    <mergeCell ref="AL93:AL94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="AK95:AK96"/>
+    <mergeCell ref="AL95:AL96"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="AK97:AK98"/>
+    <mergeCell ref="AL97:AL98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="AK99:AK100"/>
+    <mergeCell ref="AL99:AL100"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="C101:C102"/>
+    <mergeCell ref="AK101:AK102"/>
+    <mergeCell ref="AL101:AL102"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="AK103:AK104"/>
+    <mergeCell ref="AL103:AL104"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="AK105:AK106"/>
+    <mergeCell ref="AL105:AL106"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="AK107:AK108"/>
+    <mergeCell ref="AL107:AL108"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="AK109:AK110"/>
+    <mergeCell ref="AL109:AL110"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="AK111:AK112"/>
+    <mergeCell ref="AL111:AL112"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="AK113:AK114"/>
+    <mergeCell ref="AL113:AL114"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="AK115:AK116"/>
+    <mergeCell ref="AL115:AL116"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="AK117:AK118"/>
+    <mergeCell ref="AL117:AL118"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="AK119:AK120"/>
+    <mergeCell ref="AL119:AL120"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="AK121:AK122"/>
+    <mergeCell ref="AL121:AL122"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="AK123:AK124"/>
+    <mergeCell ref="AL123:AL124"/>
+    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="AK125:AK126"/>
+    <mergeCell ref="AL125:AL126"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="AK127:AK128"/>
+    <mergeCell ref="AL127:AL128"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="C129:C130"/>
+    <mergeCell ref="AK129:AK130"/>
+    <mergeCell ref="AL129:AL130"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="AK131:AK132"/>
+    <mergeCell ref="AL131:AL132"/>
+    <mergeCell ref="A133:A134"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="AK133:AK134"/>
+    <mergeCell ref="AL133:AL134"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="B135:B136"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="AK135:AK136"/>
+    <mergeCell ref="AL135:AL136"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="AK137:AK138"/>
+    <mergeCell ref="AL137:AL138"/>
+    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="AK139:AK140"/>
+    <mergeCell ref="AL139:AL140"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="AK141:AK142"/>
+    <mergeCell ref="AL141:AL142"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="AK143:AK144"/>
+    <mergeCell ref="AL143:AL144"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="AK145:AK146"/>
+    <mergeCell ref="AL145:AL146"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="C147:C148"/>
+    <mergeCell ref="AK147:AK148"/>
+    <mergeCell ref="AL147:AL148"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="AK149:AK150"/>
+    <mergeCell ref="AL149:AL150"/>
+    <mergeCell ref="A151:A152"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="C151:C152"/>
+    <mergeCell ref="AK151:AK152"/>
+    <mergeCell ref="AL151:AL152"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="C153:C154"/>
+    <mergeCell ref="AK153:AK154"/>
+    <mergeCell ref="AL153:AL154"/>
+    <mergeCell ref="A155:A156"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="C155:C156"/>
+    <mergeCell ref="AK155:AK156"/>
+    <mergeCell ref="AL155:AL156"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="AK157:AK158"/>
+    <mergeCell ref="AL157:AL158"/>
+    <mergeCell ref="A159:A160"/>
+    <mergeCell ref="B159:B160"/>
+    <mergeCell ref="C159:C160"/>
+    <mergeCell ref="AK159:AK160"/>
+    <mergeCell ref="AL159:AL160"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="AK162:AK163"/>
+    <mergeCell ref="AL162:AL163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="AK164:AK165"/>
+    <mergeCell ref="AL164:AL165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="AK166:AK167"/>
+    <mergeCell ref="AL166:AL167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="AK168:AK169"/>
+    <mergeCell ref="AL168:AL169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="AK170:AK171"/>
+    <mergeCell ref="AL170:AL171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="AK172:AK173"/>
+    <mergeCell ref="AL172:AL173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="AK174:AK175"/>
+    <mergeCell ref="AL174:AL175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="AK176:AK177"/>
+    <mergeCell ref="AL176:AL177"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="AK178:AK179"/>
+    <mergeCell ref="AL178:AL179"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="AK180:AK181"/>
+    <mergeCell ref="AL180:AL181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="C182:C183"/>
+    <mergeCell ref="AK182:AK183"/>
+    <mergeCell ref="AL182:AL183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="AK184:AK185"/>
+    <mergeCell ref="AL184:AL185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="AK186:AK187"/>
+    <mergeCell ref="AL186:AL187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="AK188:AK189"/>
+    <mergeCell ref="AL188:AL189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="AK190:AK191"/>
+    <mergeCell ref="AL190:AL191"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="C192:C193"/>
+    <mergeCell ref="AK192:AK193"/>
+    <mergeCell ref="AL192:AL193"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="C194:C195"/>
+    <mergeCell ref="AK194:AK195"/>
+    <mergeCell ref="AL194:AL195"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="AK196:AK197"/>
+    <mergeCell ref="AL196:AL197"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="AK198:AK199"/>
+    <mergeCell ref="AL198:AL199"/>
+    <mergeCell ref="A200:A201"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="AK200:AK201"/>
+    <mergeCell ref="AL200:AL201"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="AK202:AK203"/>
+    <mergeCell ref="AL202:AL203"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="AK204:AK205"/>
+    <mergeCell ref="AL204:AL205"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.9055118110236221" right="0.19685039370078741" top="0.27559055118110237" bottom="0.31496062992125984" header="0.6692913385826772" footer="0.39370078740157483"/>
